--- a/Experimental_data.xlsx
+++ b/Experimental_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="PE_Normal"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="19">
   <si>
     <t>Time (hours)</t>
   </si>
@@ -58,6 +58,9 @@
     <t>Ammonia-deficient (repetition)</t>
   </si>
   <si>
+    <t>N (original)</t>
+  </si>
+  <si>
     <t>Time (Hours)</t>
   </si>
   <si>
@@ -83,7 +86,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -153,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="32">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -185,7 +192,25 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
@@ -212,8 +237,23 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -517,563 +557,579 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="16" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="17" width="13.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="17" width="12.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="17" width="12.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="17" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="17" width="12.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="17" width="12.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="17" width="14.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="17" width="12.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="17" width="12.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="17" width="12.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="17" width="12.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="17" width="12.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="18" width="13.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="18" width="12.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="19" width="12.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="24" width="12.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="30" width="13.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="30" width="16.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="30" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="30" width="13.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="30" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="30" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="30" width="15.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="30" width="15.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="30" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="30" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="30" width="15.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="30" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="31" width="13.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="31" width="13.290714285714287" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="F1" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="I1" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="13"/>
+      <c r="O1" s="26" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="4">
         <v>0</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="27">
         <v>0.228519</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="27">
         <v>274981.8993164774</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="27">
         <v>0.0011010000000000002</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="27">
         <v>5.389066666666667</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="27">
         <v>26.989574736966443</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="27">
         <v>0.1111325684836706</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="27">
         <v>0.9507718666666666</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="27">
         <v>866.3250567232511</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="27">
         <v>0.01961547976576436</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="27">
         <v>7.156666666666666</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="27">
         <v>30000.00000000128</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="27">
         <v>0.0033333333333332624</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="27">
         <f>10^-K2</f>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="27">
         <v>0.00776378486929085</v>
       </c>
-      <c r="P2" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="5">
         <v>3.5</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="27">
         <v>0.234024</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="27">
         <v>1</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="27">
         <v>0</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="27">
         <v>5.336833333333334</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="27">
         <v>61.815993157381655</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="27">
         <v>0.07343260704739946</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="27">
         <v>0.9060905666666667</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="27">
         <v>281.8480451553724</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="27">
         <v>0.03438997492396747</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="27">
         <v>7.133333333333333</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="27">
         <v>7500.00000000032</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="27">
         <v>0.006666666666666525</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N3" s="27">
         <f>10^-K3</f>
       </c>
-      <c r="O3" s="5">
+      <c r="O3" s="27">
         <v>0.100931477902668</v>
       </c>
-      <c r="P3" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="4">
         <v>7</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="27">
         <v>0.27476100000000003</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="27">
         <v>274981.8993164774</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="27">
         <v>0.0011010000000000002</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="27">
         <v>5.513633333333334</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="27">
         <v>392.6398354053797</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="27">
         <v>0.029136822826870593</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="27">
         <v>0.9503526</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="27">
         <v>180.00148783408602</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="27">
         <v>0.04303297044178258</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="27">
         <v>7.066666666666666</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="27">
         <v>29999.999999995947</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="27">
         <v>0.0033333333333335586</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4" s="27">
         <f>10^-K4</f>
       </c>
-      <c r="O4" s="5">
+      <c r="O4" s="27">
         <v>0.293478233055139</v>
       </c>
-      <c r="P4" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="4">
         <v>16</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="27">
         <v>0.565425</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="27">
         <v>2749.8189931647744</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="27">
         <v>0.011010000000000002</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="27">
         <v>4.751833333333334</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="27">
         <v>64.51107913273023</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="27">
         <v>0.07188234213707226</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="27">
         <v>0.9042199333333333</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="27">
         <v>1329.3132097492294</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="27">
         <v>0.015835278738977443</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="27">
         <v>6.696666666666666</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="27">
         <v>1578.947368421061</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="27">
         <v>0.01452966314513554</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N5" s="27">
         <f>10^-K5</f>
       </c>
-      <c r="O5" s="5">
+      <c r="O5" s="27">
         <v>1.67236008994913</v>
       </c>
-      <c r="P5" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="5">
         <v>19.5</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="27">
         <v>0.8351699999999999</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="27">
         <v>3666.4253242197233</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="27">
         <v>0.00953493969566664</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="27">
         <v>4.433533333333333</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="27">
         <v>23.962976243185217</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="27">
         <v>0.11794213741397849</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="27">
         <v>0.9334535333333333</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="27">
         <v>552.7568485761628</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="27">
         <v>0.02455683016028559</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="27">
         <v>6.513333333333333</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="27">
         <v>7500.00000000032</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="27">
         <v>0.006666666666666525</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="27">
         <f>10^-K6</f>
       </c>
-      <c r="O6" s="5">
+      <c r="O6" s="27">
         <v>2.6288819279753</v>
       </c>
-      <c r="P6" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="4">
         <v>23</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="27">
         <v>1.02234</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="27">
         <v>180.31599955178834</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="27">
         <v>0.042995424465866156</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="27">
         <v>3.930066666666667</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="27">
         <v>10.698745404487646</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="27">
         <v>0.1765114758623674</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="27">
         <v>0.9368756666666666</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="27">
         <v>631.0361611826196</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="27">
         <v>0.022983292762231513</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="27">
         <v>6.363333333333333</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="27">
         <v>2307.692307692296</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="27">
         <v>0.012018504251546663</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="27">
         <f>10^-K7</f>
       </c>
-      <c r="O7" s="5">
+      <c r="O7" s="27">
         <v>3.3059004025761</v>
       </c>
-      <c r="P7" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="4">
         <v>24</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="27">
         <v>1.06638</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="27">
         <v>916.6063310549247</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="27">
         <v>0.019069879391333342</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="27">
         <v>3.8788</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="27">
         <v>24.114183552824695</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="27">
         <v>0.11757177949377694</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="27">
         <v>0.9113481333333334</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="27">
         <v>11232.366445934198</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="27">
         <v>0.005447581557086704</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="27">
         <v>6.41</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="27">
         <v>10000.000000000426</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="27">
         <v>0.005773502691896135</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8" s="27">
         <f>10^-K8</f>
       </c>
-      <c r="O8" s="5">
+      <c r="O8" s="27">
         <v>3.31832285642229</v>
       </c>
-      <c r="P8" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="5">
         <v>27.5</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="27">
         <v>1.2370349999999999</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="27">
         <v>255.7971156432352</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="27">
         <v>0.03609869907628249</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="27">
         <v>3.5394</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="27">
         <v>51.87881730822608</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="27">
         <v>0.08015753239714904</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="27">
         <v>0.9227773666666667</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="27">
         <v>667.9835477964043</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="27">
         <v>0.022338627671691095</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="27">
         <v>6.349999999999999</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9" s="27">
         <v>9999.999999999538</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="27">
         <v>0.0057735026918963915</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9" s="27">
         <f>10^-K9</f>
       </c>
-      <c r="O9" s="5">
+      <c r="O9" s="27">
         <v>3.33074516810587</v>
       </c>
-      <c r="P9" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="4">
         <v>31</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="27">
         <v>1.446225</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="27">
         <v>523.7750463170993</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="27">
         <v>0.025227079200731917</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="27">
         <v>3.2052333333333336</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="27">
         <v>56.593597415408176</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="27">
         <v>0.07674599519048388</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="27">
         <v>0.8364228666666667</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="27">
         <v>314.404712933345</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="27">
         <v>0.03256078366902601</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="27">
         <v>6.29</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="27">
         <v>10000.000000000426</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="27">
         <v>0.005773502691896135</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N10" s="27">
         <f>10^-K10</f>
       </c>
-      <c r="O10" s="5">
+      <c r="O10" s="27">
         <v>3.34937870671255</v>
       </c>
-      <c r="P10" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="6"/>
+      <c r="A11" s="5">
+        <v>40</v>
+      </c>
+      <c r="B11" s="27">
+        <v>1.1874900000000002</v>
+      </c>
+      <c r="C11" s="27">
+        <v>392.8312847378241</v>
+      </c>
+      <c r="D11" s="27">
+        <v>0.029129721934821176</v>
+      </c>
+      <c r="E11" s="27">
+        <v>3.885866666666667</v>
+      </c>
+      <c r="F11" s="27">
+        <v>6.722364895702947</v>
+      </c>
+      <c r="G11" s="27">
+        <v>0.2226785226384541</v>
+      </c>
+      <c r="H11" s="27">
+        <v>0.90749</v>
+      </c>
+      <c r="I11" s="27">
+        <v>631.4888749500838</v>
+      </c>
+      <c r="J11" s="27">
+        <v>0.022975052934940832</v>
+      </c>
+      <c r="K11" s="27">
+        <v>6.326666666666667</v>
+      </c>
+      <c r="L11" s="27">
+        <v>1874.9999999999966</v>
+      </c>
+      <c r="M11" s="27">
+        <v>0.013333333333333346</v>
+      </c>
+      <c r="N11" s="27">
+        <f>10^-K11</f>
+      </c>
+      <c r="O11" s="27">
+        <v>3.36801224531922</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="14"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="13"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="14"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="13"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="14"/>
+      <c r="A14" s="21"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -1086,9 +1142,8 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="13"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1494,32 +1549,32 @@
   <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="19" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="22" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="24" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="24" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="25" width="14.147857142857141" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="12" t="s">
-        <v>11</v>
+      <c r="A1" s="18" t="s">
+        <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -1528,7 +1583,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>2</v>
@@ -1537,7 +1592,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>2</v>
@@ -1546,7 +1601,7 @@
         <v>5</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>2</v>
@@ -1555,7 +1610,7 @@
         <v>6</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
@@ -1601,7 +1656,7 @@
       <c r="N2" s="5">
         <f>10^-K2</f>
       </c>
-      <c r="O2" s="13"/>
+      <c r="O2" s="19"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="5">
@@ -1646,7 +1701,7 @@
       <c r="N3" s="5">
         <f>10^-K3</f>
       </c>
-      <c r="O3" s="13"/>
+      <c r="O3" s="19"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="4">
@@ -1691,7 +1746,7 @@
       <c r="N4" s="5">
         <f>10^-K4</f>
       </c>
-      <c r="O4" s="13"/>
+      <c r="O4" s="19"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="4">
@@ -1736,7 +1791,7 @@
       <c r="N5" s="5">
         <f>10^-K5</f>
       </c>
-      <c r="O5" s="13"/>
+      <c r="O5" s="19"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="5">
@@ -1781,7 +1836,7 @@
       <c r="N6" s="5">
         <f>10^-K6</f>
       </c>
-      <c r="O6" s="13"/>
+      <c r="O6" s="19"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="4">
@@ -1826,7 +1881,7 @@
       <c r="N7" s="5">
         <f>10^-K7</f>
       </c>
-      <c r="O7" s="13"/>
+      <c r="O7" s="19"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="4">
@@ -1871,7 +1926,7 @@
       <c r="N8" s="5">
         <f>10^-K8</f>
       </c>
-      <c r="O8" s="13"/>
+      <c r="O8" s="19"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="5">
@@ -1916,7 +1971,7 @@
       <c r="N9" s="5">
         <f>10^-K9</f>
       </c>
-      <c r="O9" s="13"/>
+      <c r="O9" s="19"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="4">
@@ -1961,7 +2016,7 @@
       <c r="N10" s="5">
         <f>10^-K10</f>
       </c>
-      <c r="O10" s="13"/>
+      <c r="O10" s="19"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="4">
@@ -2007,11 +2062,11 @@
         <f>10^-K11</f>
       </c>
       <c r="O11" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="14"/>
+      <c r="A12" s="20"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -2023,9 +2078,9 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="13"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2058,14 +2113,14 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="12" t="s">
-        <v>11</v>
+      <c r="A1" s="18" t="s">
+        <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -2074,7 +2129,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>2</v>
@@ -2083,7 +2138,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>2</v>
@@ -2092,7 +2147,7 @@
         <v>5</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>2</v>
@@ -2101,7 +2156,7 @@
         <v>6</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
@@ -2553,7 +2608,7 @@
         <f>10^-K11</f>
       </c>
       <c r="O11" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2587,14 +2642,14 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="12" t="s">
-        <v>11</v>
+      <c r="A1" s="18" t="s">
+        <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -2603,7 +2658,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>2</v>
@@ -2612,7 +2667,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>2</v>
@@ -2621,7 +2676,7 @@
         <v>5</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>2</v>
@@ -2630,7 +2685,7 @@
         <v>6</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
@@ -3082,7 +3137,7 @@
         <f>10^-K11</f>
       </c>
       <c r="O11" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -3116,14 +3171,14 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="12" t="s">
-        <v>11</v>
+      <c r="A1" s="18" t="s">
+        <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -3132,7 +3187,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>2</v>
@@ -3141,7 +3196,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>2</v>
@@ -3150,7 +3205,7 @@
         <v>5</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>2</v>
@@ -3159,7 +3214,7 @@
         <v>6</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
@@ -3611,7 +3666,7 @@
         <f>10^-K11</f>
       </c>
       <c r="O11" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -3624,24 +3679,25 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -3656,7 +3712,7 @@
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="11" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -3668,10 +3724,13 @@
       <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="12" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="3"/>
+      <c r="L1" s="11" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="4">
@@ -3689,7 +3748,7 @@
       <c r="E2" s="5">
         <v>0.067418131422077</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="13">
         <v>1.0266189000000001</v>
       </c>
       <c r="G2" s="5">
@@ -3701,10 +3760,13 @@
       <c r="I2" s="5">
         <v>0.006666666666666821</v>
       </c>
-      <c r="J2" s="5">
-        <f>10^-G2</f>
+      <c r="J2" s="14">
+        <f>10^-H2</f>
       </c>
       <c r="K2" s="3"/>
+      <c r="L2" s="13">
+        <v>1.0266189000000001</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="4">
@@ -3722,7 +3784,7 @@
       <c r="E3" s="5">
         <v>0.044008572397255016</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="13">
         <v>0.9814482666666665</v>
       </c>
       <c r="G3" s="5">
@@ -3734,10 +3796,13 @@
       <c r="I3" s="5">
         <v>0.0033333333333332624</v>
       </c>
-      <c r="J3" s="5">
-        <f>10^-G3</f>
+      <c r="J3" s="14">
+        <f>10^-H3</f>
       </c>
       <c r="K3" s="3"/>
+      <c r="L3" s="13">
+        <v>0.9814482666666665</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="4">
@@ -3755,7 +3820,7 @@
       <c r="E4" s="5">
         <v>0.030120996737233625</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="13">
         <v>0.9563208</v>
       </c>
       <c r="G4" s="5">
@@ -3767,10 +3832,13 @@
       <c r="I4" s="5">
         <v>6.2803698347351e-16</v>
       </c>
-      <c r="J4" s="5">
-        <f>10^-G4</f>
+      <c r="J4" s="14">
+        <f>10^-H4</f>
       </c>
       <c r="K4" s="3"/>
+      <c r="L4" s="13">
+        <v>0.9563208</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="5">
@@ -3788,7 +3856,7 @@
       <c r="E5" s="5">
         <v>0.02594635491419437</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="13">
         <v>0.9399317666666667</v>
       </c>
       <c r="G5" s="5">
@@ -3800,10 +3868,13 @@
       <c r="I5" s="5">
         <v>6.2803698347351e-16</v>
       </c>
-      <c r="J5" s="5">
-        <f>10^-G5</f>
+      <c r="J5" s="14">
+        <f>10^-H5</f>
       </c>
       <c r="K5" s="3"/>
+      <c r="L5" s="13">
+        <v>0.9399317666666667</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="4">
@@ -3821,8 +3892,8 @@
       <c r="E6" s="5">
         <v>0.0675168456345856</v>
       </c>
-      <c r="F6" s="11">
-        <v>0.92</v>
+      <c r="F6" s="15">
+        <v>0.9689079666666668</v>
       </c>
       <c r="G6" s="5">
         <v>0.012248600656038687</v>
@@ -3833,10 +3904,13 @@
       <c r="I6" s="5">
         <v>0.006666666666666821</v>
       </c>
-      <c r="J6" s="5">
-        <f>10^-G6</f>
+      <c r="J6" s="14">
+        <f>10^-H6</f>
       </c>
       <c r="K6" s="3"/>
+      <c r="L6" s="15">
+        <v>0.9689079666666668</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="5">
@@ -3854,8 +3928,8 @@
       <c r="E7" s="5">
         <v>0.09620250054500204</v>
       </c>
-      <c r="F7" s="11">
-        <v>0.91</v>
+      <c r="F7" s="15">
+        <f>AVERAGE(F6,F8)</f>
       </c>
       <c r="G7" s="5">
         <v>0.14177843598383005</v>
@@ -3866,10 +3940,13 @@
       <c r="I7" s="5">
         <v>0.0033333333333332624</v>
       </c>
-      <c r="J7" s="5">
-        <f>10^-G7</f>
+      <c r="J7" s="14">
+        <f>10^-H7</f>
       </c>
       <c r="K7" s="3"/>
+      <c r="L7" s="15">
+        <v>1.0654959333333334</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="4">
@@ -3887,7 +3964,7 @@
       <c r="E8" s="5">
         <v>0.03272289378673253</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="13">
         <v>0.8997685</v>
       </c>
       <c r="G8" s="5">
@@ -3899,10 +3976,13 @@
       <c r="I8" s="5">
         <v>6.2803698347351e-16</v>
       </c>
-      <c r="J8" s="5">
-        <f>10^-G8</f>
+      <c r="J8" s="14">
+        <f>10^-H8</f>
       </c>
       <c r="K8" s="3"/>
+      <c r="L8" s="13">
+        <v>0.8997685</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="5">
@@ -3920,8 +4000,8 @@
       <c r="E9" s="5">
         <v>0.04058883261850885</v>
       </c>
-      <c r="F9" s="5">
-        <v>0.9</v>
+      <c r="F9" s="15">
+        <v>0.9534774666666667</v>
       </c>
       <c r="G9" s="5">
         <v>0.0007209760891396707</v>
@@ -3932,10 +4012,13 @@
       <c r="I9" s="5">
         <v>0.006666666666666821</v>
       </c>
-      <c r="J9" s="5">
-        <f>10^-G9</f>
+      <c r="J9" s="14">
+        <f>10^-H9</f>
       </c>
       <c r="K9" s="3"/>
+      <c r="L9" s="15">
+        <v>0.9534774666666667</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="4">
@@ -3953,8 +4036,8 @@
       <c r="E10" s="5">
         <v>0.026439427628701346</v>
       </c>
-      <c r="F10" s="5">
-        <v>0.9</v>
+      <c r="F10" s="15">
+        <v>0.9278216666666665</v>
       </c>
       <c r="G10" s="5">
         <v>0.0035484659602582165</v>
@@ -3965,23 +4048,49 @@
       <c r="I10" s="5">
         <v>0.00881917103688206</v>
       </c>
-      <c r="J10" s="5">
-        <f>10^-G10</f>
+      <c r="J10" s="14">
+        <f>10^-H10</f>
       </c>
       <c r="K10" s="3"/>
+      <c r="L10" s="15">
+        <v>0.9278216666666665</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
+      <c r="A11" s="5">
+        <v>99.5</v>
+      </c>
+      <c r="B11" s="5">
+        <v>1.192995</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0.030650542817379306</v>
+      </c>
+      <c r="D11" s="5">
+        <v>3.2709333333333332</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.16515569758396006</v>
+      </c>
+      <c r="F11" s="13">
+        <v>0.9482218666666666</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.017242691340713382</v>
+      </c>
+      <c r="H11" s="5">
+        <v>6.383333333333333</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0.0033333333333332624</v>
+      </c>
+      <c r="J11" s="14">
+        <f>10^-H11</f>
+      </c>
       <c r="K11" s="6"/>
+      <c r="L11" s="13">
+        <v>0.9482218666666666</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Experimental_data.xlsx
+++ b/Experimental_data.xlsx
@@ -1,24 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/02ff00bc61bfec36/DAE Model Analysis/DAE_System_Model_Calibration_and_Validation/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9595CCCB5F96CA554F11C8179BBD7EA587F59ABE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="5"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="PE_Normal"/>
-    <sheet r:id="rId2" sheetId="2" name="PE_Amm_def"/>
-    <sheet r:id="rId3" sheetId="3" name="PE_pH_55"/>
-    <sheet r:id="rId4" sheetId="4" name="PE_Glyc_def"/>
-    <sheet r:id="rId5" sheetId="5" name="PE_pH_46"/>
-    <sheet r:id="rId6" sheetId="6" name="V_Normal"/>
-    <sheet r:id="rId7" sheetId="7" name="V_Amm_def_rep"/>
-    <sheet r:id="rId8" sheetId="8" name="V_Amm_Glyc_def"/>
-    <sheet r:id="rId9" sheetId="9" name="V_Glyc_def"/>
-    <sheet r:id="rId10" sheetId="10" name="V_Amm_def"/>
+    <sheet name="PE_Normal" sheetId="1" r:id="rId1"/>
+    <sheet name="PE_Amm_def" sheetId="2" r:id="rId2"/>
+    <sheet name="PE_pH_55" sheetId="3" r:id="rId3"/>
+    <sheet name="PE_Glyc_def" sheetId="4" r:id="rId4"/>
+    <sheet name="PE_pH_46" sheetId="5" r:id="rId5"/>
+    <sheet name="V_Normal" sheetId="6" r:id="rId6"/>
+    <sheet name="V_Amm_def_rep" sheetId="7" r:id="rId7"/>
+    <sheet name="V_Amm_Glyc_def" sheetId="8" r:id="rId8"/>
+    <sheet name="V_Glyc_def" sheetId="9" r:id="rId9"/>
+    <sheet name="V_Amm_def" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -85,7 +104,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.000000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000000"/>
@@ -122,7 +141,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffff00"/>
+        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,16 +162,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -160,110 +179,86 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="25">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -274,10 +269,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -315,71 +310,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -407,7 +402,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -430,11 +425,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -443,13 +438,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -459,7 +454,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -468,7 +463,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -477,7 +472,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -485,10 +480,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -553,583 +548,557 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="24" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="30" width="13.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="30" width="16.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="30" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="30" width="13.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="30" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="30" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="30" width="15.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="30" width="15.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="30" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="30" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="30" width="15.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="30" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="31" width="13.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="31" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="12.5703125" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="15.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" style="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row r="1" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="J1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="26" t="s">
+      <c r="L1" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="26" t="s">
+      <c r="M1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="26" t="s">
+      <c r="N1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="26" t="s">
+      <c r="O1" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>0</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="22">
         <v>0.228519</v>
       </c>
-      <c r="C2" s="27">
-        <v>274981.8993164774</v>
-      </c>
-      <c r="D2" s="27">
-        <v>0.0011010000000000002</v>
-      </c>
-      <c r="E2" s="27">
-        <v>5.389066666666667</v>
-      </c>
-      <c r="F2" s="27">
+      <c r="C2" s="22">
+        <v>274981.89931647741</v>
+      </c>
+      <c r="D2" s="22">
+        <v>1.1010000000000002E-3</v>
+      </c>
+      <c r="E2" s="22">
+        <v>5.3890666666666673</v>
+      </c>
+      <c r="F2" s="22">
         <v>26.989574736966443</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="22">
         <v>0.1111325684836706</v>
       </c>
-      <c r="H2" s="27">
-        <v>0.9507718666666666</v>
-      </c>
-      <c r="I2" s="27">
-        <v>866.3250567232511</v>
-      </c>
-      <c r="J2" s="27">
-        <v>0.01961547976576436</v>
-      </c>
-      <c r="K2" s="27">
-        <v>7.156666666666666</v>
-      </c>
-      <c r="L2" s="27">
-        <v>30000.00000000128</v>
-      </c>
-      <c r="M2" s="27">
-        <v>0.0033333333333332624</v>
-      </c>
-      <c r="N2" s="27">
-        <f>10^-K2</f>
-      </c>
-      <c r="O2" s="27">
-        <v>0.00776378486929085</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="H2" s="22">
+        <v>0.95077186666666658</v>
+      </c>
+      <c r="I2" s="22">
+        <v>866.32505672325112</v>
+      </c>
+      <c r="J2" s="22">
+        <v>1.961547976576436E-2</v>
+      </c>
+      <c r="K2" s="22">
+        <v>7.1566666666666663</v>
+      </c>
+      <c r="L2" s="22">
+        <v>30000.000000001281</v>
+      </c>
+      <c r="M2" s="22">
+        <v>3.3333333333332624E-3</v>
+      </c>
+      <c r="N2" s="22">
+        <f t="shared" ref="N2:N11" si="0">10^-K2</f>
+        <v>6.9716139996346712E-8</v>
+      </c>
+      <c r="O2" s="22">
+        <v>7.7637848692908504E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>3.5</v>
       </c>
-      <c r="B3" s="27">
-        <v>0.234024</v>
-      </c>
-      <c r="C3" s="27">
+      <c r="B3" s="22">
+        <v>0.23402400000000001</v>
+      </c>
+      <c r="C3" s="22">
         <v>1</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="22">
         <v>0</v>
       </c>
-      <c r="E3" s="27">
-        <v>5.336833333333334</v>
-      </c>
-      <c r="F3" s="27">
+      <c r="E3" s="22">
+        <v>5.3368333333333338</v>
+      </c>
+      <c r="F3" s="22">
         <v>61.815993157381655</v>
       </c>
-      <c r="G3" s="27">
-        <v>0.07343260704739946</v>
-      </c>
-      <c r="H3" s="27">
-        <v>0.9060905666666667</v>
-      </c>
-      <c r="I3" s="27">
+      <c r="G3" s="22">
+        <v>7.3432607047399456E-2</v>
+      </c>
+      <c r="H3" s="22">
+        <v>0.90609056666666665</v>
+      </c>
+      <c r="I3" s="22">
         <v>281.8480451553724</v>
       </c>
-      <c r="J3" s="27">
-        <v>0.03438997492396747</v>
-      </c>
-      <c r="K3" s="27">
-        <v>7.133333333333333</v>
-      </c>
-      <c r="L3" s="27">
-        <v>7500.00000000032</v>
-      </c>
-      <c r="M3" s="27">
-        <v>0.006666666666666525</v>
-      </c>
-      <c r="N3" s="27">
-        <f>10^-K3</f>
-      </c>
-      <c r="O3" s="27">
+      <c r="J3" s="22">
+        <v>3.4389974923967469E-2</v>
+      </c>
+      <c r="K3" s="22">
+        <v>7.1333333333333329</v>
+      </c>
+      <c r="L3" s="22">
+        <v>7500.0000000003201</v>
+      </c>
+      <c r="M3" s="22">
+        <v>6.6666666666665248E-3</v>
+      </c>
+      <c r="N3" s="22">
+        <f t="shared" si="0"/>
+        <v>7.3564225445964003E-8</v>
+      </c>
+      <c r="O3" s="22">
         <v>0.100931477902668</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>7</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="22">
         <v>0.27476100000000003</v>
       </c>
-      <c r="C4" s="27">
-        <v>274981.8993164774</v>
-      </c>
-      <c r="D4" s="27">
-        <v>0.0011010000000000002</v>
-      </c>
-      <c r="E4" s="27">
-        <v>5.513633333333334</v>
-      </c>
-      <c r="F4" s="27">
+      <c r="C4" s="22">
+        <v>274981.89931647741</v>
+      </c>
+      <c r="D4" s="22">
+        <v>1.1010000000000002E-3</v>
+      </c>
+      <c r="E4" s="22">
+        <v>5.5136333333333338</v>
+      </c>
+      <c r="F4" s="22">
         <v>392.6398354053797</v>
       </c>
-      <c r="G4" s="27">
-        <v>0.029136822826870593</v>
-      </c>
-      <c r="H4" s="27">
-        <v>0.9503526</v>
-      </c>
-      <c r="I4" s="27">
+      <c r="G4" s="22">
+        <v>2.9136822826870593E-2</v>
+      </c>
+      <c r="H4" s="22">
+        <v>0.95035259999999999</v>
+      </c>
+      <c r="I4" s="22">
         <v>180.00148783408602</v>
       </c>
-      <c r="J4" s="27">
-        <v>0.04303297044178258</v>
-      </c>
-      <c r="K4" s="27">
-        <v>7.066666666666666</v>
-      </c>
-      <c r="L4" s="27">
+      <c r="J4" s="22">
+        <v>4.303297044178258E-2</v>
+      </c>
+      <c r="K4" s="22">
+        <v>7.0666666666666664</v>
+      </c>
+      <c r="L4" s="22">
         <v>29999.999999995947</v>
       </c>
-      <c r="M4" s="27">
-        <v>0.0033333333333335586</v>
-      </c>
-      <c r="N4" s="27">
-        <f>10^-K4</f>
-      </c>
-      <c r="O4" s="27">
-        <v>0.293478233055139</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="M4" s="22">
+        <v>3.3333333333335586E-3</v>
+      </c>
+      <c r="N4" s="22">
+        <f t="shared" si="0"/>
+        <v>8.5769589859089308E-8</v>
+      </c>
+      <c r="O4" s="22">
+        <v>0.29347823305513898</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>16</v>
       </c>
-      <c r="B5" s="27">
-        <v>0.565425</v>
-      </c>
-      <c r="C5" s="27">
+      <c r="B5" s="22">
+        <v>0.56542499999999996</v>
+      </c>
+      <c r="C5" s="22">
         <v>2749.8189931647744</v>
       </c>
-      <c r="D5" s="27">
-        <v>0.011010000000000002</v>
-      </c>
-      <c r="E5" s="27">
-        <v>4.751833333333334</v>
-      </c>
-      <c r="F5" s="27">
-        <v>64.51107913273023</v>
-      </c>
-      <c r="G5" s="27">
-        <v>0.07188234213707226</v>
-      </c>
-      <c r="H5" s="27">
-        <v>0.9042199333333333</v>
-      </c>
-      <c r="I5" s="27">
+      <c r="D5" s="22">
+        <v>1.1010000000000002E-2</v>
+      </c>
+      <c r="E5" s="22">
+        <v>4.7518333333333338</v>
+      </c>
+      <c r="F5" s="22">
+        <v>64.511079132730231</v>
+      </c>
+      <c r="G5" s="22">
+        <v>7.1882342137072258E-2</v>
+      </c>
+      <c r="H5" s="22">
+        <v>0.90421993333333328</v>
+      </c>
+      <c r="I5" s="22">
         <v>1329.3132097492294</v>
       </c>
-      <c r="J5" s="27">
-        <v>0.015835278738977443</v>
-      </c>
-      <c r="K5" s="27">
-        <v>6.696666666666666</v>
-      </c>
-      <c r="L5" s="27">
-        <v>1578.947368421061</v>
-      </c>
-      <c r="M5" s="27">
-        <v>0.01452966314513554</v>
-      </c>
-      <c r="N5" s="27">
-        <f>10^-K5</f>
-      </c>
-      <c r="O5" s="27">
+      <c r="J5" s="22">
+        <v>1.5835278738977443E-2</v>
+      </c>
+      <c r="K5" s="22">
+        <v>6.6966666666666663</v>
+      </c>
+      <c r="L5" s="22">
+        <v>1578.9473684210609</v>
+      </c>
+      <c r="M5" s="22">
+        <v>1.4529663145135541E-2</v>
+      </c>
+      <c r="N5" s="22">
+        <f t="shared" si="0"/>
+        <v>2.0106354402584853E-7</v>
+      </c>
+      <c r="O5" s="22">
         <v>1.67236008994913</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+    <row r="6" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>19.5</v>
       </c>
-      <c r="B6" s="27">
-        <v>0.8351699999999999</v>
-      </c>
-      <c r="C6" s="27">
+      <c r="B6" s="22">
+        <v>0.83516999999999986</v>
+      </c>
+      <c r="C6" s="22">
         <v>3666.4253242197233</v>
       </c>
-      <c r="D6" s="27">
-        <v>0.00953493969566664</v>
-      </c>
-      <c r="E6" s="27">
-        <v>4.433533333333333</v>
-      </c>
-      <c r="F6" s="27">
+      <c r="D6" s="22">
+        <v>9.5349396956666398E-3</v>
+      </c>
+      <c r="E6" s="22">
+        <v>4.4335333333333331</v>
+      </c>
+      <c r="F6" s="22">
         <v>23.962976243185217</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="22">
         <v>0.11794213741397849</v>
       </c>
-      <c r="H6" s="27">
-        <v>0.9334535333333333</v>
-      </c>
-      <c r="I6" s="27">
-        <v>552.7568485761628</v>
-      </c>
-      <c r="J6" s="27">
-        <v>0.02455683016028559</v>
-      </c>
-      <c r="K6" s="27">
-        <v>6.513333333333333</v>
-      </c>
-      <c r="L6" s="27">
-        <v>7500.00000000032</v>
-      </c>
-      <c r="M6" s="27">
-        <v>0.006666666666666525</v>
-      </c>
-      <c r="N6" s="27">
-        <f>10^-K6</f>
-      </c>
-      <c r="O6" s="27">
+      <c r="H6" s="22">
+        <v>0.93345353333333325</v>
+      </c>
+      <c r="I6" s="22">
+        <v>552.75684857616284</v>
+      </c>
+      <c r="J6" s="22">
+        <v>2.4556830160285589E-2</v>
+      </c>
+      <c r="K6" s="22">
+        <v>6.5133333333333328</v>
+      </c>
+      <c r="L6" s="22">
+        <v>7500.0000000003201</v>
+      </c>
+      <c r="M6" s="22">
+        <v>6.6666666666665248E-3</v>
+      </c>
+      <c r="N6" s="22">
+        <f t="shared" si="0"/>
+        <v>3.066667330713181E-7</v>
+      </c>
+      <c r="O6" s="22">
         <v>2.6288819279753</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+    <row r="7" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>23</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="22">
         <v>1.02234</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="22">
         <v>180.31599955178834</v>
       </c>
-      <c r="D7" s="27">
-        <v>0.042995424465866156</v>
-      </c>
-      <c r="E7" s="27">
-        <v>3.930066666666667</v>
-      </c>
-      <c r="F7" s="27">
+      <c r="D7" s="22">
+        <v>4.2995424465866156E-2</v>
+      </c>
+      <c r="E7" s="22">
+        <v>3.9300666666666668</v>
+      </c>
+      <c r="F7" s="22">
         <v>10.698745404487646</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="22">
         <v>0.1765114758623674</v>
       </c>
-      <c r="H7" s="27">
-        <v>0.9368756666666666</v>
-      </c>
-      <c r="I7" s="27">
-        <v>631.0361611826196</v>
-      </c>
-      <c r="J7" s="27">
-        <v>0.022983292762231513</v>
-      </c>
-      <c r="K7" s="27">
-        <v>6.363333333333333</v>
-      </c>
-      <c r="L7" s="27">
-        <v>2307.692307692296</v>
-      </c>
-      <c r="M7" s="27">
-        <v>0.012018504251546663</v>
-      </c>
-      <c r="N7" s="27">
-        <f>10^-K7</f>
-      </c>
-      <c r="O7" s="27">
-        <v>3.3059004025761</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="H7" s="22">
+        <v>0.93687566666666655</v>
+      </c>
+      <c r="I7" s="22">
+        <v>631.03616118261959</v>
+      </c>
+      <c r="J7" s="22">
+        <v>2.2983292762231513E-2</v>
+      </c>
+      <c r="K7" s="22">
+        <v>6.3633333333333333</v>
+      </c>
+      <c r="L7" s="22">
+        <v>2307.6923076922958</v>
+      </c>
+      <c r="M7" s="22">
+        <v>1.2018504251546663E-2</v>
+      </c>
+      <c r="N7" s="22">
+        <f t="shared" si="0"/>
+        <v>4.3317827415004061E-7</v>
+      </c>
+      <c r="O7" s="22">
+        <v>3.3059004025760999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>24</v>
       </c>
-      <c r="B8" s="27">
-        <v>1.06638</v>
-      </c>
-      <c r="C8" s="27">
-        <v>916.6063310549247</v>
-      </c>
-      <c r="D8" s="27">
-        <v>0.019069879391333342</v>
-      </c>
-      <c r="E8" s="27">
+      <c r="B8" s="22">
+        <v>1.0663800000000001</v>
+      </c>
+      <c r="C8" s="22">
+        <v>916.60633105492468</v>
+      </c>
+      <c r="D8" s="22">
+        <v>1.9069879391333342E-2</v>
+      </c>
+      <c r="E8" s="22">
         <v>3.8788</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="22">
         <v>24.114183552824695</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="22">
         <v>0.11757177949377694</v>
       </c>
-      <c r="H8" s="27">
-        <v>0.9113481333333334</v>
-      </c>
-      <c r="I8" s="27">
+      <c r="H8" s="22">
+        <v>0.91134813333333342</v>
+      </c>
+      <c r="I8" s="22">
         <v>11232.366445934198</v>
       </c>
-      <c r="J8" s="27">
-        <v>0.005447581557086704</v>
-      </c>
-      <c r="K8" s="27">
+      <c r="J8" s="22">
+        <v>5.447581557086704E-3</v>
+      </c>
+      <c r="K8" s="22">
         <v>6.41</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="22">
         <v>10000.000000000426</v>
       </c>
-      <c r="M8" s="27">
-        <v>0.005773502691896135</v>
-      </c>
-      <c r="N8" s="27">
-        <f>10^-K8</f>
-      </c>
-      <c r="O8" s="27">
-        <v>3.31832285642229</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+      <c r="M8" s="22">
+        <v>5.7735026918961348E-3</v>
+      </c>
+      <c r="N8" s="22">
+        <f t="shared" si="0"/>
+        <v>3.8904514499428027E-7</v>
+      </c>
+      <c r="O8" s="22">
+        <v>3.3183228564222902</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>27.5</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="22">
         <v>1.2370349999999999</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="22">
         <v>255.7971156432352</v>
       </c>
-      <c r="D9" s="27">
-        <v>0.03609869907628249</v>
-      </c>
-      <c r="E9" s="27">
-        <v>3.5394</v>
-      </c>
-      <c r="F9" s="27">
-        <v>51.87881730822608</v>
-      </c>
-      <c r="G9" s="27">
-        <v>0.08015753239714904</v>
-      </c>
-      <c r="H9" s="27">
-        <v>0.9227773666666667</v>
-      </c>
-      <c r="I9" s="27">
-        <v>667.9835477964043</v>
-      </c>
-      <c r="J9" s="27">
-        <v>0.022338627671691095</v>
-      </c>
-      <c r="K9" s="27">
-        <v>6.349999999999999</v>
-      </c>
-      <c r="L9" s="27">
+      <c r="D9" s="22">
+        <v>3.6098699076282492E-2</v>
+      </c>
+      <c r="E9" s="22">
+        <v>3.5394000000000001</v>
+      </c>
+      <c r="F9" s="22">
+        <v>51.878817308226083</v>
+      </c>
+      <c r="G9" s="22">
+        <v>8.0157532397149039E-2</v>
+      </c>
+      <c r="H9" s="22">
+        <v>0.92277736666666665</v>
+      </c>
+      <c r="I9" s="22">
+        <v>667.98354779640431</v>
+      </c>
+      <c r="J9" s="22">
+        <v>2.2338627671691095E-2</v>
+      </c>
+      <c r="K9" s="22">
+        <v>6.3499999999999988</v>
+      </c>
+      <c r="L9" s="22">
         <v>9999.999999999538</v>
       </c>
-      <c r="M9" s="27">
-        <v>0.0057735026918963915</v>
-      </c>
-      <c r="N9" s="27">
-        <f>10^-K9</f>
-      </c>
-      <c r="O9" s="27">
+      <c r="M9" s="22">
+        <v>5.7735026918963915E-3</v>
+      </c>
+      <c r="N9" s="22">
+        <f t="shared" si="0"/>
+        <v>4.4668359215096402E-7</v>
+      </c>
+      <c r="O9" s="22">
         <v>3.33074516810587</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+    <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>31</v>
       </c>
-      <c r="B10" s="27">
-        <v>1.446225</v>
-      </c>
-      <c r="C10" s="27">
-        <v>523.7750463170993</v>
-      </c>
-      <c r="D10" s="27">
-        <v>0.025227079200731917</v>
-      </c>
-      <c r="E10" s="27">
+      <c r="B10" s="22">
+        <v>1.4462250000000001</v>
+      </c>
+      <c r="C10" s="22">
+        <v>523.77504631709928</v>
+      </c>
+      <c r="D10" s="22">
+        <v>2.5227079200731917E-2</v>
+      </c>
+      <c r="E10" s="22">
         <v>3.2052333333333336</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="22">
         <v>56.593597415408176</v>
       </c>
-      <c r="G10" s="27">
-        <v>0.07674599519048388</v>
-      </c>
-      <c r="H10" s="27">
-        <v>0.8364228666666667</v>
-      </c>
-      <c r="I10" s="27">
-        <v>314.404712933345</v>
-      </c>
-      <c r="J10" s="27">
-        <v>0.03256078366902601</v>
-      </c>
-      <c r="K10" s="27">
+      <c r="G10" s="22">
+        <v>7.6745995190483876E-2</v>
+      </c>
+      <c r="H10" s="22">
+        <v>0.83642286666666665</v>
+      </c>
+      <c r="I10" s="22">
+        <v>314.40471293334502</v>
+      </c>
+      <c r="J10" s="22">
+        <v>3.2560783669026011E-2</v>
+      </c>
+      <c r="K10" s="22">
         <v>6.29</v>
       </c>
-      <c r="L10" s="27">
+      <c r="L10" s="22">
         <v>10000.000000000426</v>
       </c>
-      <c r="M10" s="27">
-        <v>0.005773502691896135</v>
-      </c>
-      <c r="N10" s="27">
-        <f>10^-K10</f>
-      </c>
-      <c r="O10" s="27">
+      <c r="M10" s="22">
+        <v>5.7735026918961348E-3</v>
+      </c>
+      <c r="N10" s="22">
+        <f t="shared" si="0"/>
+        <v>5.1286138399136375E-7</v>
+      </c>
+      <c r="O10" s="22">
         <v>3.34937870671255</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+    <row r="11" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>40</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="22">
         <v>1.1874900000000002</v>
       </c>
-      <c r="C11" s="27">
-        <v>392.8312847378241</v>
-      </c>
-      <c r="D11" s="27">
-        <v>0.029129721934821176</v>
-      </c>
-      <c r="E11" s="27">
-        <v>3.885866666666667</v>
-      </c>
-      <c r="F11" s="27">
-        <v>6.722364895702947</v>
-      </c>
-      <c r="G11" s="27">
-        <v>0.2226785226384541</v>
-      </c>
-      <c r="H11" s="27">
-        <v>0.90749</v>
-      </c>
-      <c r="I11" s="27">
-        <v>631.4888749500838</v>
-      </c>
-      <c r="J11" s="27">
-        <v>0.022975052934940832</v>
-      </c>
-      <c r="K11" s="27">
-        <v>6.326666666666667</v>
-      </c>
-      <c r="L11" s="27">
+      <c r="C11" s="22">
+        <v>392.83128473782409</v>
+      </c>
+      <c r="D11" s="22">
+        <v>2.9129721934821176E-2</v>
+      </c>
+      <c r="E11" s="22">
+        <v>3.8858666666666668</v>
+      </c>
+      <c r="F11" s="22">
+        <v>6.7223648957029472</v>
+      </c>
+      <c r="G11" s="22">
+        <v>0.22267852263845411</v>
+      </c>
+      <c r="H11" s="22">
+        <v>0.90749000000000002</v>
+      </c>
+      <c r="I11" s="22">
+        <v>631.48887495008375</v>
+      </c>
+      <c r="J11" s="22">
+        <v>2.2975052934940832E-2</v>
+      </c>
+      <c r="K11" s="22">
+        <v>6.3266666666666671</v>
+      </c>
+      <c r="L11" s="22">
         <v>1874.9999999999966</v>
       </c>
-      <c r="M11" s="27">
-        <v>0.013333333333333346</v>
-      </c>
-      <c r="N11" s="27">
-        <f>10^-K11</f>
-      </c>
-      <c r="O11" s="27">
-        <v>3.36801224531922</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="21"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-      <c r="M12" s="28"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="29"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="21"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="21"/>
+      <c r="M11" s="22">
+        <v>1.3333333333333346E-2</v>
+      </c>
+      <c r="N11" s="22">
+        <f t="shared" si="0"/>
+        <v>4.7133895361573911E-7</v>
+      </c>
+      <c r="O11" s="22">
+        <v>3.3680122453192198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -1142,8 +1111,6 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1151,27 +1118,18 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="10" width="14.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row r="1" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1202,108 +1160,107 @@
       <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    </row>
+    <row r="2" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>0</v>
       </c>
       <c r="B2" s="5">
-        <v>0.227418</v>
+        <v>0.22741800000000001</v>
       </c>
       <c r="C2" s="4">
         <v>0</v>
       </c>
       <c r="D2" s="5">
-        <v>5.3526</v>
+        <v>5.3525999999999998</v>
       </c>
       <c r="E2" s="5">
-        <v>0.129352013255818</v>
+        <v>0.12935201325581799</v>
       </c>
       <c r="F2" s="5">
-        <v>0.027794933333333337</v>
+        <v>2.7794933333333337E-2</v>
       </c>
       <c r="G2" s="5">
-        <v>0.0010745121564898384</v>
+        <v>1.0745121564898384E-3</v>
       </c>
       <c r="H2" s="5">
-        <v>7.136666666666667</v>
+        <v>7.1366666666666667</v>
       </c>
       <c r="I2" s="5">
-        <v>0.0033333333333332624</v>
+        <v>3.3333333333332624E-3</v>
       </c>
       <c r="J2" s="5">
-        <f>10^-G2</f>
-      </c>
-      <c r="K2" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+        <f t="shared" ref="J2:J11" si="0">10^-G2</f>
+        <v>0.99752890252670001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>7</v>
       </c>
       <c r="B3" s="5">
-        <v>0.253842</v>
+        <v>0.25384200000000001</v>
       </c>
       <c r="C3" s="4">
         <v>0</v>
       </c>
       <c r="D3" s="5">
-        <v>5.128733333333334</v>
+        <v>5.1287333333333338</v>
       </c>
       <c r="E3" s="5">
         <v>0.17107133339958247</v>
       </c>
       <c r="F3" s="5">
-        <v>0.025435700000000002</v>
+        <v>2.5435700000000002E-2</v>
       </c>
       <c r="G3" s="5">
-        <v>0.0005539606694823501</v>
+        <v>5.5396066948235013E-4</v>
       </c>
       <c r="H3" s="5">
         <v>7.04</v>
       </c>
       <c r="I3" s="5">
-        <v>0.005773502691896135</v>
+        <v>5.7735026918961348E-3</v>
       </c>
       <c r="J3" s="5">
-        <f>10^-G3</f>
-      </c>
-      <c r="K3" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.99872527157773028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>24</v>
       </c>
       <c r="B4" s="5">
-        <v>0.7966350000000001</v>
+        <v>0.79663500000000009</v>
       </c>
       <c r="C4" s="5">
-        <v>0.011010000000000002</v>
+        <v>1.1010000000000002E-2</v>
       </c>
       <c r="D4" s="5">
-        <v>4.428466666666666</v>
+        <v>4.4284666666666661</v>
       </c>
       <c r="E4" s="5">
         <v>0.12185009004692786</v>
       </c>
       <c r="F4" s="5">
-        <v>0.00014073333333333333</v>
+        <v>1.4073333333333333E-4</v>
       </c>
       <c r="G4" s="5">
-        <v>0.000073404912036669</v>
+        <v>7.3404912036668997E-5</v>
       </c>
       <c r="H4" s="5">
-        <v>6.776666666666666</v>
+        <v>6.7766666666666664</v>
       </c>
       <c r="I4" s="5">
-        <v>0.006666666666666821</v>
+        <v>6.6666666666668206E-3</v>
       </c>
       <c r="J4" s="5">
-        <f>10^-G4</f>
-      </c>
-      <c r="K4" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.99983099322704583</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>31</v>
       </c>
@@ -1311,7 +1268,7 @@
         <v>0.82416</v>
       </c>
       <c r="C5" s="5">
-        <v>0.019848559771429235</v>
+        <v>1.9848559771429235E-2</v>
       </c>
       <c r="D5" s="5">
         <v>3.8183333333333334</v>
@@ -1323,20 +1280,20 @@
         <v>0.27749913333333337</v>
       </c>
       <c r="G5" s="5">
-        <v>0.006008801045226167</v>
+        <v>6.0088010452261668E-3</v>
       </c>
       <c r="H5" s="5">
-        <v>6.510000000000001</v>
+        <v>6.5100000000000007</v>
       </c>
       <c r="I5" s="5">
-        <v>0.009999999999999787</v>
+        <v>9.9999999999997868E-3</v>
       </c>
       <c r="J5" s="5">
-        <f>10^-G5</f>
-      </c>
-      <c r="K5" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.98625949872654717</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>48</v>
       </c>
@@ -1344,7 +1301,7 @@
         <v>0.9232499999999999</v>
       </c>
       <c r="C6" s="5">
-        <v>0.0558696480658327</v>
+        <v>5.5869648065832701E-2</v>
       </c>
       <c r="D6" s="5">
         <v>3.8808000000000002</v>
@@ -1356,28 +1313,28 @@
         <v>0.25966910000000004</v>
       </c>
       <c r="G6" s="5">
-        <v>0.006357279721180542</v>
+        <v>6.3572797211805419E-3</v>
       </c>
       <c r="H6" s="5">
         <v>6.5</v>
       </c>
       <c r="I6" s="5">
-        <v>0.005773502691896135</v>
+        <v>5.7735026918961348E-3</v>
       </c>
       <c r="J6" s="5">
-        <f>10^-G6</f>
-      </c>
-      <c r="K6" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.98546843974110698</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>55</v>
       </c>
       <c r="B7" s="5">
-        <v>1.00032</v>
+        <v>1.0003200000000001</v>
       </c>
       <c r="C7" s="5">
-        <v>0.028604819087000046</v>
+        <v>2.8604819087000046E-2</v>
       </c>
       <c r="D7" s="5">
         <v>3.4951000000000003</v>
@@ -1386,23 +1343,23 @@
         <v>0.1292088361271525</v>
       </c>
       <c r="F7" s="5">
-        <v>0.251149</v>
+        <v>0.25114900000000001</v>
       </c>
       <c r="G7" s="5">
-        <v>0.00753964889832412</v>
+        <v>7.5396488983241203E-3</v>
       </c>
       <c r="H7" s="5">
-        <v>6.423333333333333</v>
+        <v>6.4233333333333329</v>
       </c>
       <c r="I7" s="5">
-        <v>0.0033333333333332624</v>
+        <v>3.3333333333332624E-3</v>
       </c>
       <c r="J7" s="5">
-        <f>10^-G7</f>
-      </c>
-      <c r="K7" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.98278914520635052</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>72</v>
       </c>
@@ -1410,73 +1367,73 @@
         <v>1.0939050000000001</v>
       </c>
       <c r="C8" s="5">
-        <v>0.005505000000000019</v>
+        <v>5.5050000000000194E-3</v>
       </c>
       <c r="D8" s="5">
-        <v>3.108333333333333</v>
+        <v>3.1083333333333329</v>
       </c>
       <c r="E8" s="5">
-        <v>0.09647625499457255</v>
+        <v>9.6476254994572547E-2</v>
       </c>
       <c r="F8" s="5">
         <v>0.24546040000000002</v>
       </c>
       <c r="G8" s="5">
-        <v>0.0007572503703091461</v>
+        <v>7.5725037030914609E-4</v>
       </c>
       <c r="H8" s="5">
-        <v>5.253333333333334</v>
+        <v>5.2533333333333339</v>
       </c>
       <c r="I8" s="5">
-        <v>0.05925462944877068</v>
+        <v>5.9254629448770683E-2</v>
       </c>
       <c r="J8" s="5">
-        <f>10^-G8</f>
-      </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.99825788583127295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>79</v>
       </c>
       <c r="B9" s="5">
-        <v>1.226025</v>
+        <v>1.2260249999999999</v>
       </c>
       <c r="C9" s="5">
-        <v>0.03969711954285852</v>
+        <v>3.9697119542858518E-2</v>
       </c>
       <c r="D9" s="5">
-        <v>2.6904</v>
+        <v>2.6903999999999999</v>
       </c>
       <c r="E9" s="5">
-        <v>0.0819270610563649</v>
+        <v>8.1927061056364894E-2</v>
       </c>
       <c r="F9" s="5">
         <v>0.22824369999999997</v>
       </c>
       <c r="G9" s="5">
-        <v>0.007692103988073317</v>
+        <v>7.6921039880733172E-3</v>
       </c>
       <c r="H9" s="5">
         <v>5.18</v>
       </c>
       <c r="I9" s="5">
-        <v>0.05859465277082297</v>
+        <v>5.8594652770822972E-2</v>
       </c>
       <c r="J9" s="5">
-        <f>10^-G9</f>
-      </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.98244420664916954</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>96</v>
       </c>
       <c r="B10" s="5">
-        <v>1.07739</v>
+        <v>1.0773900000000001</v>
       </c>
       <c r="C10" s="5">
-        <v>0.029129721934821107</v>
+        <v>2.9129721934821107E-2</v>
       </c>
       <c r="D10" s="5">
         <v>2.7253000000000003</v>
@@ -1488,20 +1445,20 @@
         <v>0.24084593333333335</v>
       </c>
       <c r="G10" s="5">
-        <v>0.0040676969750844385</v>
+        <v>4.0676969750844385E-3</v>
       </c>
       <c r="H10" s="5">
         <v>5.206666666666667</v>
       </c>
       <c r="I10" s="5">
-        <v>0.05238744548500561</v>
+        <v>5.238744548500561E-2</v>
       </c>
       <c r="J10" s="5">
-        <f>10^-G10</f>
-      </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.99067750798258458</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>99.5</v>
       </c>
@@ -1509,28 +1466,29 @@
         <v>1.17648</v>
       </c>
       <c r="C11" s="5">
-        <v>0.030650542817379306</v>
+        <v>3.0650542817379306E-2</v>
       </c>
       <c r="D11" s="5">
         <v>2.466366666666667</v>
       </c>
       <c r="E11" s="5">
-        <v>0.036488826295791525</v>
+        <v>3.6488826295791525E-2</v>
       </c>
       <c r="F11" s="5">
         <v>0.24374193333333335</v>
       </c>
       <c r="G11" s="5">
-        <v>0.005637436399148499</v>
+        <v>5.637436399148499E-3</v>
       </c>
       <c r="H11" s="5">
-        <v>5.153333333333333</v>
+        <v>5.1533333333333333</v>
       </c>
       <c r="I11" s="5">
-        <v>0.06119186583561939</v>
+        <v>6.1191865835619391E-2</v>
       </c>
       <c r="J11" s="5">
-        <f>10^-G11</f>
+        <f t="shared" si="0"/>
+        <v>0.98710320861612477</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>7</v>
@@ -1542,32 +1500,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="22" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="23" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="24" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="24" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="25" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="14.140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="12" width="14.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1613,7 +1560,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>0</v>
       </c>
@@ -1630,35 +1577,35 @@
         <v>6.0567666666666655</v>
       </c>
       <c r="F2" s="5">
-        <v>0.7150689684854252</v>
+        <v>0.71506896848542523</v>
       </c>
       <c r="G2" s="5">
-        <v>0.6827558136780071</v>
+        <v>0.68275581367800708</v>
       </c>
       <c r="H2" s="5">
-        <v>0.036256533333333334</v>
+        <v>3.6256533333333334E-2</v>
       </c>
       <c r="I2" s="5">
         <v>24073168.95264056</v>
       </c>
       <c r="J2" s="5">
-        <v>0.00011767189317948845</v>
+        <v>1.1767189317948845E-4</v>
       </c>
       <c r="K2" s="5">
-        <v>6.900000000000001</v>
+        <v>6.9000000000000012</v>
       </c>
       <c r="L2" s="4">
         <v>1</v>
       </c>
       <c r="M2" s="5">
-        <v>6.2803698347351e-16</v>
+        <v>6.2803698347350997E-16</v>
       </c>
       <c r="N2" s="5">
-        <f>10^-K2</f>
-      </c>
-      <c r="O2" s="19"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+        <f t="shared" ref="N2:N11" si="0">10^-K2</f>
+        <v>1.2589254117941609E-7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>3.5</v>
       </c>
@@ -1666,89 +1613,89 @@
         <v>0.23622600000000002</v>
       </c>
       <c r="C3" s="5">
-        <v>274981.8993164774</v>
+        <v>274981.89931647741</v>
       </c>
       <c r="D3" s="5">
-        <v>0.0011010000000000002</v>
+        <v>1.1010000000000002E-3</v>
       </c>
       <c r="E3" s="5">
         <v>5.753333333333333</v>
       </c>
       <c r="F3" s="5">
-        <v>3.426264436622308</v>
+        <v>3.4262644366223078</v>
       </c>
       <c r="G3" s="5">
         <v>0.31190973765569496</v>
       </c>
       <c r="H3" s="5">
-        <v>0.034843000000000006</v>
+        <v>3.4843000000000006E-2</v>
       </c>
       <c r="I3" s="5">
         <v>1773873.8991715466</v>
       </c>
       <c r="J3" s="5">
-        <v>0.00043348891950467893</v>
+        <v>4.3348891950467893E-4</v>
       </c>
       <c r="K3" s="5">
-        <v>6.906666666666666</v>
+        <v>6.9066666666666663</v>
       </c>
       <c r="L3" s="5">
-        <v>7500.00000000032</v>
+        <v>7500.0000000003201</v>
       </c>
       <c r="M3" s="5">
-        <v>0.006666666666666525</v>
+        <v>6.6666666666665248E-3</v>
       </c>
       <c r="N3" s="5">
-        <f>10^-K3</f>
-      </c>
-      <c r="O3" s="19"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>1.2397477630289433E-7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>7</v>
       </c>
       <c r="B4" s="5">
-        <v>0.259347</v>
+        <v>0.25934699999999999</v>
       </c>
       <c r="C4" s="5">
-        <v>68745.47482911935</v>
+        <v>68745.474829119354</v>
       </c>
       <c r="D4" s="5">
-        <v>0.0022020000000000004</v>
+        <v>2.2020000000000004E-3</v>
       </c>
       <c r="E4" s="5">
-        <v>6.1946</v>
+        <v>6.1946000000000003</v>
       </c>
       <c r="F4" s="5">
         <v>1.2108622676137277</v>
       </c>
       <c r="G4" s="5">
-        <v>0.5246769672855878</v>
+        <v>0.52467696728558777</v>
       </c>
       <c r="H4" s="5">
-        <v>0.0320045</v>
+        <v>3.2004499999999998E-2</v>
       </c>
       <c r="I4" s="5">
         <v>2072988.9457449864</v>
       </c>
       <c r="J4" s="5">
-        <v>0.00040099677471687147</v>
+        <v>4.0099677471687147E-4</v>
       </c>
       <c r="K4" s="5">
         <v>6.836666666666666</v>
       </c>
       <c r="L4" s="5">
-        <v>30000.00000000128</v>
+        <v>30000.000000001281</v>
       </c>
       <c r="M4" s="5">
-        <v>0.0033333333333332624</v>
+        <v>3.3333333333332624E-3</v>
       </c>
       <c r="N4" s="5">
-        <f>10^-K4</f>
-      </c>
-      <c r="O4" s="19"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>1.4565766155244583E-7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>16</v>
       </c>
@@ -1759,46 +1706,46 @@
         <v>10999.275972659098</v>
       </c>
       <c r="D5" s="5">
-        <v>0.005505000000000001</v>
+        <v>5.5050000000000012E-3</v>
       </c>
       <c r="E5" s="5">
         <v>5.0930333333333335</v>
       </c>
       <c r="F5" s="5">
-        <v>0.5709479007223914</v>
+        <v>0.57094790072239143</v>
       </c>
       <c r="G5" s="5">
-        <v>0.7640840471513007</v>
+        <v>0.76408404715130074</v>
       </c>
       <c r="H5" s="5">
-        <v>0.010801066666666666</v>
+        <v>1.0801066666666666E-2</v>
       </c>
       <c r="I5" s="5">
         <v>1866572.7390672592</v>
       </c>
       <c r="J5" s="5">
-        <v>0.00042258775945884264</v>
+        <v>4.2258775945884264E-4</v>
       </c>
       <c r="K5" s="5">
-        <v>6.663333333333333</v>
+        <v>6.6633333333333331</v>
       </c>
       <c r="L5" s="5">
-        <v>2307.692307692296</v>
+        <v>2307.6923076922958</v>
       </c>
       <c r="M5" s="5">
-        <v>0.012018504251546663</v>
+        <v>1.2018504251546663E-2</v>
       </c>
       <c r="N5" s="5">
-        <f>10^-K5</f>
-      </c>
-      <c r="O5" s="19"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>2.1710342088869529E-7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>19.5</v>
       </c>
       <c r="B6" s="5">
-        <v>0.60396</v>
+        <v>0.60396000000000005</v>
       </c>
       <c r="C6" s="4">
         <v>1</v>
@@ -1807,38 +1754,38 @@
         <v>0</v>
       </c>
       <c r="E6" s="5">
-        <v>4.7663</v>
+        <v>4.7663000000000002</v>
       </c>
       <c r="F6" s="5">
-        <v>19.79058787347554</v>
+        <v>19.790587873475541</v>
       </c>
       <c r="G6" s="5">
         <v>0.12978067395931256</v>
       </c>
       <c r="H6" s="5">
-        <v>0.00002326666666666667</v>
+        <v>2.3266666666666669E-5</v>
       </c>
       <c r="I6" s="5">
-        <v>615758491.3095951</v>
+        <v>615758491.30959511</v>
       </c>
       <c r="J6" s="5">
-        <v>0.00002326666666666667</v>
+        <v>2.3266666666666669E-5</v>
       </c>
       <c r="K6" s="5">
         <v>6.543333333333333</v>
       </c>
       <c r="L6" s="5">
-        <v>2307.692307692296</v>
+        <v>2307.6923076922958</v>
       </c>
       <c r="M6" s="5">
-        <v>0.012018504251546661</v>
+        <v>1.2018504251546661E-2</v>
       </c>
       <c r="N6" s="5">
-        <f>10^-K6</f>
-      </c>
-      <c r="O6" s="19"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>2.8619804755017058E-7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>23</v>
       </c>
@@ -1846,28 +1793,28 @@
         <v>0.7195649999999999</v>
       </c>
       <c r="C7" s="5">
-        <v>916.6063310549248</v>
+        <v>916.60633105492479</v>
       </c>
       <c r="D7" s="5">
-        <v>0.019069879391333342</v>
+        <v>1.9069879391333342E-2</v>
       </c>
       <c r="E7" s="5">
-        <v>4.3124</v>
+        <v>4.3124000000000002</v>
       </c>
       <c r="F7" s="5">
         <v>13.701822849406422</v>
       </c>
       <c r="G7" s="5">
-        <v>0.155973277625795</v>
+        <v>0.15597327762579499</v>
       </c>
       <c r="H7" s="5">
-        <v>0.00006566666666666666</v>
+        <v>6.5666666666666659E-5</v>
       </c>
       <c r="I7" s="5">
         <v>305574597.38000345</v>
       </c>
       <c r="J7" s="5">
-        <v>0.00003302788384246122</v>
+        <v>3.3027883842461222E-5</v>
       </c>
       <c r="K7" s="5">
         <v>6.47</v>
@@ -1876,31 +1823,31 @@
         <v>1111.1111111111256</v>
       </c>
       <c r="M7" s="5">
-        <v>0.017320508075688662</v>
+        <v>1.7320508075688662E-2</v>
       </c>
       <c r="N7" s="5">
-        <f>10^-K7</f>
-      </c>
-      <c r="O7" s="19"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>3.3884415613920242E-7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>24</v>
       </c>
       <c r="B8" s="5">
-        <v>0.8792099999999999</v>
+        <v>0.87920999999999994</v>
       </c>
       <c r="C8" s="5">
         <v>10999.275972659172</v>
       </c>
       <c r="D8" s="5">
-        <v>0.005504999999999982</v>
+        <v>5.5049999999999821E-3</v>
       </c>
       <c r="E8" s="5">
-        <v>4.122733333333333</v>
+        <v>4.1227333333333327</v>
       </c>
       <c r="F8" s="5">
-        <v>9.519587964308785</v>
+        <v>9.5195879643087853</v>
       </c>
       <c r="G8" s="5">
         <v>0.18712434665513492</v>
@@ -1915,20 +1862,20 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>6.533333333333332</v>
+        <v>6.5333333333333323</v>
       </c>
       <c r="L8" s="5">
         <v>7499.9999999996535</v>
       </c>
       <c r="M8" s="5">
-        <v>0.006666666666666821</v>
+        <v>6.6666666666668206E-3</v>
       </c>
       <c r="N8" s="5">
-        <f>10^-K8</f>
-      </c>
-      <c r="O8" s="19"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>2.928644564625241E-7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>27.5</v>
       </c>
@@ -1936,13 +1883,13 @@
         <v>1.005825</v>
       </c>
       <c r="C9" s="5">
-        <v>354.8153539567438</v>
+        <v>354.81535395674382</v>
       </c>
       <c r="D9" s="5">
-        <v>0.03065054281737933</v>
+        <v>3.065054281737933E-2</v>
       </c>
       <c r="E9" s="5">
-        <v>3.885066666666667</v>
+        <v>3.8850666666666669</v>
       </c>
       <c r="F9" s="5">
         <v>27.738140488688682</v>
@@ -1951,29 +1898,29 @@
         <v>0.10962275209908659</v>
       </c>
       <c r="H9" s="5">
-        <v>0.000022066666666666667</v>
+        <v>2.2066666666666667E-5</v>
       </c>
       <c r="I9" s="5">
-        <v>684550159.2720039</v>
+        <v>684550159.27200389</v>
       </c>
       <c r="J9" s="5">
-        <v>0.000022066666666666667</v>
+        <v>2.2066666666666667E-5</v>
       </c>
       <c r="K9" s="5">
-        <v>6.473333333333333</v>
+        <v>6.4733333333333327</v>
       </c>
       <c r="L9" s="5">
         <v>29999.999999995947</v>
       </c>
       <c r="M9" s="5">
-        <v>0.0033333333333335586</v>
+        <v>3.3333333333335586E-3</v>
       </c>
       <c r="N9" s="5">
-        <f>10^-K9</f>
-      </c>
-      <c r="O9" s="19"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>3.3625338629516293E-7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>31</v>
       </c>
@@ -1984,16 +1931,16 @@
         <v>144.7273154297248</v>
       </c>
       <c r="D10" s="5">
-        <v>0.04799147736838286</v>
+        <v>4.7991477368382857E-2</v>
       </c>
       <c r="E10" s="5">
         <v>3.7362333333333333</v>
       </c>
       <c r="F10" s="5">
-        <v>42.65233851398116</v>
+        <v>42.652338513981157</v>
       </c>
       <c r="G10" s="5">
-        <v>0.08840319250142749</v>
+        <v>8.8403192501427488E-2</v>
       </c>
       <c r="H10" s="4">
         <v>0</v>
@@ -2011,14 +1958,14 @@
         <v>9999.999999999538</v>
       </c>
       <c r="M10" s="5">
-        <v>0.0057735026918963915</v>
+        <v>5.7735026918963915E-3</v>
       </c>
       <c r="N10" s="5">
-        <f>10^-K10</f>
-      </c>
-      <c r="O10" s="19"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>3.3884415613920242E-7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>40</v>
       </c>
@@ -2029,7 +1976,7 @@
         <v>2749.818993164793</v>
       </c>
       <c r="D11" s="5">
-        <v>0.011009999999999964</v>
+        <v>1.1009999999999964E-2</v>
       </c>
       <c r="E11" s="5">
         <v>3.4233666666666664</v>
@@ -2038,35 +1985,35 @@
         <v>100.25139708676129</v>
       </c>
       <c r="G11" s="5">
-        <v>0.05766259137815819</v>
+        <v>5.7662591378158191E-2</v>
       </c>
       <c r="H11" s="5">
-        <v>0.0000245</v>
+        <v>2.4499999999999999E-5</v>
       </c>
       <c r="I11" s="5">
-        <v>555324170.4845204</v>
+        <v>555324170.48452044</v>
       </c>
       <c r="J11" s="5">
-        <v>0.000024500000000000003</v>
+        <v>2.4500000000000003E-5</v>
       </c>
       <c r="K11" s="5">
-        <v>6.426666666666667</v>
+        <v>6.4266666666666667</v>
       </c>
       <c r="L11" s="5">
-        <v>30000.00000000128</v>
+        <v>30000.000000001281</v>
       </c>
       <c r="M11" s="5">
-        <v>0.0033333333333332624</v>
+        <v>3.3333333333332624E-3</v>
       </c>
       <c r="N11" s="5">
-        <f>10^-K11</f>
+        <f t="shared" si="0"/>
+        <v>3.743978389823804E-7</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="20"/>
+    <row r="12" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -2078,9 +2025,6 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="21"/>
-      <c r="O12" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2088,32 +2032,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="14.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="14" width="14.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -2159,7 +2091,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>0</v>
       </c>
@@ -2167,44 +2099,44 @@
         <v>0.22631700000000002</v>
       </c>
       <c r="C2" s="5">
-        <v>274981.8993164774</v>
+        <v>274981.89931647741</v>
       </c>
       <c r="D2" s="5">
-        <v>0.0011010000000000002</v>
+        <v>1.1010000000000002E-3</v>
       </c>
       <c r="E2" s="5">
-        <v>5.2245</v>
+        <v>5.2244999999999999</v>
       </c>
       <c r="F2" s="5">
-        <v>3.288940421469165</v>
+        <v>3.2889404214691651</v>
       </c>
       <c r="G2" s="5">
         <v>0.31835477589213784</v>
       </c>
       <c r="H2" s="5">
-        <v>0.9738578666666667</v>
+        <v>0.97385786666666674</v>
       </c>
       <c r="I2" s="5">
         <v>1117.3556589993748</v>
       </c>
       <c r="J2" s="5">
-        <v>0.017272040839106922</v>
+        <v>1.7272040839106922E-2</v>
       </c>
       <c r="K2" s="5">
-        <v>5.353333333333334</v>
+        <v>5.3533333333333344</v>
       </c>
       <c r="L2" s="5">
         <v>29999.999999995947</v>
       </c>
       <c r="M2" s="5">
-        <v>0.0033333333333335586</v>
+        <v>3.3333333333335586E-3</v>
       </c>
       <c r="N2" s="5">
-        <f>10^-K2</f>
-      </c>
-      <c r="O2" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+        <f t="shared" ref="N2:N11" si="0">10^-K2</f>
+        <v>4.432682923460076E-6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>3.5</v>
       </c>
@@ -2212,58 +2144,58 @@
         <v>0.23512500000000003</v>
       </c>
       <c r="C3" s="5">
-        <v>274981.8993164774</v>
+        <v>274981.89931647741</v>
       </c>
       <c r="D3" s="5">
-        <v>0.0011010000000000002</v>
+        <v>1.1010000000000002E-3</v>
       </c>
       <c r="E3" s="5">
         <v>5.178866666666667</v>
       </c>
       <c r="F3" s="5">
-        <v>0.6943352489757412</v>
+        <v>0.69433524897574117</v>
       </c>
       <c r="G3" s="5">
-        <v>0.6928747994968336</v>
+        <v>0.69287479949683362</v>
       </c>
       <c r="H3" s="5">
-        <v>1.0017377</v>
+        <v>1.0017377000000001</v>
       </c>
       <c r="I3" s="5">
         <v>465.62795949480363</v>
       </c>
       <c r="J3" s="5">
-        <v>0.02675591745396393</v>
+        <v>2.675591745396393E-2</v>
       </c>
       <c r="K3" s="5">
         <v>5.336666666666666</v>
       </c>
       <c r="L3" s="5">
-        <v>7500.00000000032</v>
+        <v>7500.0000000003201</v>
       </c>
       <c r="M3" s="5">
-        <v>0.006666666666666525</v>
+        <v>6.6666666666665248E-3</v>
       </c>
       <c r="N3" s="5">
-        <f>10^-K3</f>
-      </c>
-      <c r="O3" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>4.6060996915966598E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>7</v>
       </c>
       <c r="B4" s="5">
-        <v>0.256044</v>
+        <v>0.25604399999999999</v>
       </c>
       <c r="C4" s="5">
-        <v>274981.8993164774</v>
+        <v>274981.89931647741</v>
       </c>
       <c r="D4" s="5">
-        <v>0.0011010000000000002</v>
+        <v>1.1010000000000002E-3</v>
       </c>
       <c r="E4" s="5">
-        <v>5.372633333333333</v>
+        <v>5.3726333333333329</v>
       </c>
       <c r="F4" s="5">
         <v>24.092848054117038</v>
@@ -2275,10 +2207,10 @@
         <v>1.0045819666666667</v>
       </c>
       <c r="I4" s="5">
-        <v>649.4136059416148</v>
+        <v>649.41360594161483</v>
       </c>
       <c r="J4" s="5">
-        <v>0.0226557623768092</v>
+        <v>2.2655762376809201E-2</v>
       </c>
       <c r="K4" s="5">
         <v>5.33</v>
@@ -2287,14 +2219,14 @@
         <v>10000.000000000426</v>
       </c>
       <c r="M4" s="5">
-        <v>0.005773502691896135</v>
+        <v>5.7735026918961348E-3</v>
       </c>
       <c r="N4" s="5">
-        <f>10^-K4</f>
-      </c>
-      <c r="O4" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>4.6773514128719787E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>16</v>
       </c>
@@ -2305,7 +2237,7 @@
         <v>1571.3251389512964</v>
       </c>
       <c r="D5" s="5">
-        <v>0.014564860967410588</v>
+        <v>1.4564860967410588E-2</v>
       </c>
       <c r="E5" s="5">
         <v>5.183066666666666</v>
@@ -2317,29 +2249,29 @@
         <v>0.13444778829634135</v>
       </c>
       <c r="H5" s="5">
-        <v>0.9218214666666666</v>
+        <v>0.92182146666666664</v>
       </c>
       <c r="I5" s="5">
         <v>10648.564297804034</v>
       </c>
       <c r="J5" s="5">
-        <v>0.005594919520521379</v>
+        <v>5.5949195205213789E-3</v>
       </c>
       <c r="K5" s="5">
-        <v>5.239999999999999</v>
+        <v>5.2399999999999993</v>
       </c>
       <c r="L5" s="5">
         <v>1428.5714285714532</v>
       </c>
       <c r="M5" s="5">
-        <v>0.015275252316519336</v>
+        <v>1.5275252316519336E-2</v>
       </c>
       <c r="N5" s="5">
-        <f>10^-K5</f>
-      </c>
-      <c r="O5" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>5.7543993733715718E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>19.5</v>
       </c>
@@ -2350,7 +2282,7 @@
         <v>10999.275972659098</v>
       </c>
       <c r="D6" s="5">
-        <v>0.005505000000000001</v>
+        <v>5.5050000000000012E-3</v>
       </c>
       <c r="E6" s="5">
         <v>5.1513</v>
@@ -2362,13 +2294,13 @@
         <v>0.31559488272150427</v>
       </c>
       <c r="H6" s="5">
-        <v>0.9661781333333334</v>
+        <v>0.96617813333333336</v>
       </c>
       <c r="I6" s="5">
-        <v>386.5428242866369</v>
+        <v>386.54282428663691</v>
       </c>
       <c r="J6" s="5">
-        <v>0.02936571400740059</v>
+        <v>2.9365714007400592E-2</v>
       </c>
       <c r="K6" s="5">
         <v>5.2</v>
@@ -2380,11 +2312,11 @@
         <v>0</v>
       </c>
       <c r="N6" s="5">
-        <f>10^-K6</f>
-      </c>
-      <c r="O6" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>6.3095734448019212E-6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>23</v>
       </c>
@@ -2395,7 +2327,7 @@
         <v>10999.275972659098</v>
       </c>
       <c r="D7" s="5">
-        <v>0.005505000000000001</v>
+        <v>5.5050000000000012E-3</v>
       </c>
       <c r="E7" s="5">
         <v>4.801166666666667</v>
@@ -2407,88 +2339,88 @@
         <v>0.11456733585295792</v>
       </c>
       <c r="H7" s="5">
-        <v>0.9364479333333334</v>
+        <v>0.93644793333333343</v>
       </c>
       <c r="I7" s="5">
         <v>2000.0878457649328</v>
       </c>
       <c r="J7" s="5">
-        <v>0.012909660975710327</v>
+        <v>1.2909660975710327E-2</v>
       </c>
       <c r="K7" s="5">
-        <v>5.140000000000001</v>
+        <v>5.1400000000000006</v>
       </c>
       <c r="L7" s="5">
         <v>9999.999999999538</v>
       </c>
       <c r="M7" s="5">
-        <v>0.0057735026918963915</v>
+        <v>5.7735026918963915E-3</v>
       </c>
       <c r="N7" s="5">
-        <f>10^-K7</f>
-      </c>
-      <c r="O7" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>7.244359600749883E-6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>24</v>
       </c>
       <c r="B8" s="5">
-        <v>0.565425</v>
+        <v>0.56542499999999996</v>
       </c>
       <c r="C8" s="5">
         <v>10999.275972659172</v>
       </c>
       <c r="D8" s="5">
-        <v>0.005504999999999982</v>
+        <v>5.5049999999999821E-3</v>
       </c>
       <c r="E8" s="5">
-        <v>4.856733333333334</v>
+        <v>4.8567333333333336</v>
       </c>
       <c r="F8" s="5">
-        <v>4.250395502843534</v>
+        <v>4.2503955028435341</v>
       </c>
       <c r="G8" s="5">
         <v>0.28004298677960937</v>
       </c>
       <c r="H8" s="5">
-        <v>0.9422910333333333</v>
+        <v>0.94229103333333331</v>
       </c>
       <c r="I8" s="5">
-        <v>18022.56731234424</v>
+        <v>18022.567312344239</v>
       </c>
       <c r="J8" s="5">
-        <v>0.004300619745003172</v>
+        <v>4.3006197450031723E-3</v>
       </c>
       <c r="K8" s="5">
-        <v>5.113333333333333</v>
+        <v>5.1133333333333333</v>
       </c>
       <c r="L8" s="5">
         <v>7499.9999999996535</v>
       </c>
       <c r="M8" s="5">
-        <v>0.006666666666666821</v>
+        <v>6.6666666666668206E-3</v>
       </c>
       <c r="N8" s="5">
-        <f>10^-K8</f>
-      </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>7.7031200579721349E-6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>27.5</v>
       </c>
       <c r="B9" s="5">
-        <v>0.7085549999999999</v>
+        <v>0.70855499999999993</v>
       </c>
       <c r="C9" s="5">
         <v>297.27772899078667</v>
       </c>
       <c r="D9" s="5">
-        <v>0.03348560772929169</v>
+        <v>3.348560772929169E-2</v>
       </c>
       <c r="E9" s="5">
-        <v>4.363066666666667</v>
+        <v>4.3630666666666666</v>
       </c>
       <c r="F9" s="5">
         <v>14.880677058901652</v>
@@ -2497,43 +2429,43 @@
         <v>0.14966768002626496</v>
       </c>
       <c r="H9" s="5">
-        <v>0.9071417333333334</v>
+        <v>0.90714173333333337</v>
       </c>
       <c r="I9" s="5">
         <v>1989.4279573238891</v>
       </c>
       <c r="J9" s="5">
-        <v>0.012944201480757513</v>
+        <v>1.2944201480757513E-2</v>
       </c>
       <c r="K9" s="5">
-        <v>5.033333333333334</v>
+        <v>5.0333333333333341</v>
       </c>
       <c r="L9" s="5">
-        <v>4285.714285714251</v>
+        <v>4285.7142857142508</v>
       </c>
       <c r="M9" s="5">
-        <v>0.008819171036882005</v>
+        <v>8.819171036882005E-3</v>
       </c>
       <c r="N9" s="5">
-        <f>10^-K9</f>
-      </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>9.2611872812879153E-6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>31</v>
       </c>
       <c r="B10" s="5">
-        <v>0.73608</v>
+        <v>0.73607999999999996</v>
       </c>
       <c r="C10" s="5">
         <v>3666.4253242197233</v>
       </c>
       <c r="D10" s="5">
-        <v>0.00953493969566664</v>
+        <v>9.5349396956666398E-3</v>
       </c>
       <c r="E10" s="5">
-        <v>4.293633333333333</v>
+        <v>4.2936333333333332</v>
       </c>
       <c r="F10" s="5">
         <v>1.9294333174597007</v>
@@ -2542,70 +2474,71 @@
         <v>0.41564684261735363</v>
       </c>
       <c r="H10" s="5">
-        <v>0.9385156666666665</v>
+        <v>0.93851566666666653</v>
       </c>
       <c r="I10" s="5">
         <v>14069.930423249994</v>
       </c>
       <c r="J10" s="5">
-        <v>0.0048673592040357015</v>
+        <v>4.8673592040357015E-3</v>
       </c>
       <c r="K10" s="5">
-        <v>4.946666666666666</v>
+        <v>4.9466666666666663</v>
       </c>
       <c r="L10" s="5">
-        <v>30000.00000000128</v>
+        <v>30000.000000001281</v>
       </c>
       <c r="M10" s="5">
-        <v>0.0033333333333332624</v>
+        <v>3.3333333333332624E-3</v>
       </c>
       <c r="N10" s="5">
-        <f>10^-K10</f>
-      </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>1.1306633979496388E-5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>40</v>
       </c>
       <c r="B11" s="5">
-        <v>0.8737049999999998</v>
+        <v>0.87370499999999984</v>
       </c>
       <c r="C11" s="5">
         <v>120.87116453471559</v>
       </c>
       <c r="D11" s="5">
-        <v>0.052514353038002816</v>
+        <v>5.2514353038002816E-2</v>
       </c>
       <c r="E11" s="5">
         <v>3.4417333333333335</v>
       </c>
       <c r="F11" s="5">
-        <v>8.747214850344927</v>
+        <v>8.7472148503449265</v>
       </c>
       <c r="G11" s="5">
         <v>0.19521108518159966</v>
       </c>
       <c r="H11" s="5">
-        <v>0.9533945333333333</v>
+        <v>0.95339453333333335</v>
       </c>
       <c r="I11" s="5">
         <v>12247.603175279719</v>
       </c>
       <c r="J11" s="5">
-        <v>0.00521691570321436</v>
+        <v>5.2169157032143599E-3</v>
       </c>
       <c r="K11" s="5">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="L11" s="5">
         <v>9999.999999999538</v>
       </c>
       <c r="M11" s="5">
-        <v>0.0057735026918963915</v>
+        <v>5.7735026918963915E-3</v>
       </c>
       <c r="N11" s="5">
-        <f>10^-K11</f>
+        <f t="shared" si="0"/>
+        <v>1.2589254117941658E-5</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>17</v>
@@ -2617,32 +2550,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="14.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="14" width="14.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -2688,7 +2609,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>0</v>
       </c>
@@ -2699,7 +2620,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="5">
-        <v>1.9626155733547187e-17</v>
+        <v>1.9626155733547187E-17</v>
       </c>
       <c r="E2" s="5">
         <v>1.0594666666666666</v>
@@ -2708,16 +2629,16 @@
         <v>113.65801893315282</v>
       </c>
       <c r="G2" s="5">
-        <v>0.05415509620012177</v>
+        <v>5.4155096200121773E-2</v>
       </c>
       <c r="H2" s="5">
-        <v>0.9589925</v>
+        <v>0.95899250000000003</v>
       </c>
       <c r="I2" s="5">
         <v>3453.2455884307456</v>
       </c>
       <c r="J2" s="5">
-        <v>0.009824843467964245</v>
+        <v>9.8248434679642452E-3</v>
       </c>
       <c r="K2" s="5">
         <v>6.94</v>
@@ -2729,11 +2650,11 @@
         <v>0</v>
       </c>
       <c r="N2" s="5">
-        <f>10^-K2</f>
-      </c>
-      <c r="O2" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+        <f t="shared" ref="N2:N11" si="0">10^-K2</f>
+        <v>1.1481536214968794E-7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>3.5</v>
       </c>
@@ -2741,10 +2662,10 @@
         <v>0.23952900000000002</v>
       </c>
       <c r="C3" s="5">
-        <v>274981.8993164774</v>
+        <v>274981.89931647741</v>
       </c>
       <c r="D3" s="5">
-        <v>0.0011010000000000002</v>
+        <v>1.1010000000000002E-3</v>
       </c>
       <c r="E3" s="5">
         <v>1.0296666666666667</v>
@@ -2753,16 +2674,16 @@
         <v>128.56439426242812</v>
       </c>
       <c r="G3" s="5">
-        <v>0.050918900660211104</v>
+        <v>5.0918900660211104E-2</v>
       </c>
       <c r="H3" s="5">
-        <v>0.9131758666666667</v>
+        <v>0.91317586666666672</v>
       </c>
       <c r="I3" s="5">
         <v>2150.7328065037846</v>
       </c>
       <c r="J3" s="5">
-        <v>0.012449334690969531</v>
+        <v>1.2449334690969531E-2</v>
       </c>
       <c r="K3" s="5">
         <v>6.91</v>
@@ -2774,85 +2695,85 @@
         <v>0</v>
       </c>
       <c r="N3" s="5">
-        <f>10^-K3</f>
-      </c>
-      <c r="O3" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>1.2302687708123796E-7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>7</v>
       </c>
       <c r="B4" s="5">
-        <v>0.263751</v>
+        <v>0.26375100000000001</v>
       </c>
       <c r="C4" s="5">
-        <v>91660.63310549247</v>
+        <v>91660.633105492467</v>
       </c>
       <c r="D4" s="5">
-        <v>0.0019069879391333342</v>
+        <v>1.9069879391333342E-3</v>
       </c>
       <c r="E4" s="5">
-        <v>0.9593333333333334</v>
+        <v>0.95933333333333337</v>
       </c>
       <c r="F4" s="5">
-        <v>86.45012447377101</v>
+        <v>86.450124473771012</v>
       </c>
       <c r="G4" s="5">
-        <v>0.062094989957143666</v>
+        <v>6.2094989957143666E-2</v>
       </c>
       <c r="H4" s="5">
-        <v>0.9489739</v>
+        <v>0.94897390000000004</v>
       </c>
       <c r="I4" s="5">
         <v>482.78917059515777</v>
       </c>
       <c r="J4" s="5">
-        <v>0.026276082252941205</v>
+        <v>2.6276082252941205E-2</v>
       </c>
       <c r="K4" s="5">
-        <v>6.846666666666667</v>
+        <v>6.8466666666666667</v>
       </c>
       <c r="L4" s="5">
-        <v>4285.714285714251</v>
+        <v>4285.7142857142508</v>
       </c>
       <c r="M4" s="5">
-        <v>0.008819171036882005</v>
+        <v>8.819171036882005E-3</v>
       </c>
       <c r="N4" s="5">
-        <f>10^-K4</f>
-      </c>
-      <c r="O4" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>1.4234208838643395E-7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>16</v>
       </c>
       <c r="B5" s="5">
-        <v>0.49386</v>
+        <v>0.49386000000000002</v>
       </c>
       <c r="C5" s="5">
         <v>164.16829809939205</v>
       </c>
       <c r="D5" s="5">
-        <v>0.0450603670091575</v>
+        <v>4.5060367009157498E-2</v>
       </c>
       <c r="E5" s="5">
-        <v>0.5553333333333333</v>
+        <v>0.55533333333333335</v>
       </c>
       <c r="F5" s="5">
-        <v>79.60361644536418</v>
+        <v>79.603616445364182</v>
       </c>
       <c r="G5" s="5">
-        <v>0.06471023446445273</v>
+        <v>6.4710234464452732E-2</v>
       </c>
       <c r="H5" s="5">
-        <v>0.9643681333333335</v>
+        <v>0.96436813333333349</v>
       </c>
       <c r="I5" s="5">
-        <v>299.9219577920363</v>
+        <v>299.92195779203632</v>
       </c>
       <c r="J5" s="5">
-        <v>0.033337669857651714</v>
+        <v>3.3337669857651714E-2</v>
       </c>
       <c r="K5" s="5">
         <v>6.64</v>
@@ -2861,214 +2782,214 @@
         <v>175.43859649122925</v>
       </c>
       <c r="M5" s="5">
-        <v>0.043588989435406594</v>
+        <v>4.3588989435406594E-2</v>
       </c>
       <c r="N5" s="5">
-        <f>10^-K5</f>
-      </c>
-      <c r="O5" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>2.2908676527677716E-7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>19.5</v>
       </c>
       <c r="B6" s="5">
-        <v>0.648</v>
+        <v>0.64800000000000002</v>
       </c>
       <c r="C6" s="5">
-        <v>98.2078211844571</v>
+        <v>98.207821184457103</v>
       </c>
       <c r="D6" s="5">
-        <v>0.05825944386964203</v>
+        <v>5.8259443869642033E-2</v>
       </c>
       <c r="E6" s="5">
-        <v>0.2986333333333333</v>
+        <v>0.29863333333333331</v>
       </c>
       <c r="F6" s="5">
         <v>19.07548621347847</v>
       </c>
       <c r="G6" s="5">
-        <v>0.1321909015191456</v>
+        <v>0.13219090151914559</v>
       </c>
       <c r="H6" s="5">
-        <v>0.8970824</v>
+        <v>0.89708239999999995</v>
       </c>
       <c r="I6" s="5">
         <v>481.06632179668094</v>
       </c>
       <c r="J6" s="5">
-        <v>0.026323091631746703</v>
+        <v>2.6323091631746703E-2</v>
       </c>
       <c r="K6" s="5">
-        <v>6.489999999999999</v>
+        <v>6.4899999999999993</v>
       </c>
       <c r="L6" s="5">
         <v>131.57894736842113</v>
       </c>
       <c r="M6" s="5">
-        <v>0.05033222956847166</v>
+        <v>5.0332229568471658E-2</v>
       </c>
       <c r="N6" s="5">
-        <f>10^-K6</f>
-      </c>
-      <c r="O6" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>3.2359365692962822E-7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>23</v>
       </c>
       <c r="B7" s="5">
-        <v>0.76911</v>
+        <v>0.76910999999999996</v>
       </c>
       <c r="C7" s="5">
         <v>192.96975390629967</v>
       </c>
       <c r="D7" s="5">
-        <v>0.041561838566165514</v>
+        <v>4.1561838566165514E-2</v>
       </c>
       <c r="E7" s="5">
-        <v>0.05946666666666667</v>
+        <v>5.9466666666666668E-2</v>
       </c>
       <c r="F7" s="5">
         <v>413.46860188348757</v>
       </c>
       <c r="G7" s="5">
-        <v>0.028393446035621977</v>
+        <v>2.8393446035621977E-2</v>
       </c>
       <c r="H7" s="5">
-        <v>0.8681543999999999</v>
+        <v>0.86815439999999988</v>
       </c>
       <c r="I7" s="5">
         <v>1494.223614742963</v>
       </c>
       <c r="J7" s="5">
-        <v>0.014935906106092115</v>
+        <v>1.4935906106092115E-2</v>
       </c>
       <c r="K7" s="5">
-        <v>6.433333333333334</v>
+        <v>6.4333333333333336</v>
       </c>
       <c r="L7" s="5">
-        <v>1578.947368421061</v>
+        <v>1578.9473684210609</v>
       </c>
       <c r="M7" s="5">
-        <v>0.01452966314513554</v>
+        <v>1.4529663145135541E-2</v>
       </c>
       <c r="N7" s="5">
-        <f>10^-K7</f>
-      </c>
-      <c r="O7" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>3.6869450645195708E-7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>24</v>
       </c>
       <c r="B8" s="5">
-        <v>0.72507</v>
+        <v>0.72506999999999999</v>
       </c>
       <c r="C8" s="5">
-        <v>846.098151743007</v>
+        <v>846.09815174300695</v>
       </c>
       <c r="D8" s="5">
-        <v>0.01984855977142927</v>
+        <v>1.9848559771429269E-2</v>
       </c>
       <c r="E8" s="5">
-        <v>0.018166666666666668</v>
+        <v>1.8166666666666668E-2</v>
       </c>
       <c r="F8" s="5">
         <v>110091.743119266</v>
       </c>
       <c r="G8" s="5">
-        <v>0.0017400510848184256</v>
+        <v>1.7400510848184256E-3</v>
       </c>
       <c r="H8" s="5">
         <v>0.9190436666666667</v>
       </c>
       <c r="I8" s="5">
-        <v>1128.838275887328</v>
+        <v>1128.8382758873281</v>
       </c>
       <c r="J8" s="5">
-        <v>0.017183970135985587</v>
+        <v>1.7183970135985587E-2</v>
       </c>
       <c r="K8" s="5">
-        <v>6.463333333333334</v>
+        <v>6.4633333333333338</v>
       </c>
       <c r="L8" s="5">
-        <v>1578.947368421061</v>
+        <v>1578.9473684210609</v>
       </c>
       <c r="M8" s="5">
-        <v>0.01452966314513554</v>
+        <v>1.4529663145135541E-2</v>
       </c>
       <c r="N8" s="5">
-        <f>10^-K8</f>
-      </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>3.440857338265124E-7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>27.5</v>
       </c>
       <c r="B9" s="5">
-        <v>0.7580999999999999</v>
+        <v>0.75809999999999989</v>
       </c>
       <c r="C9" s="5">
         <v>2749.8189931647744</v>
       </c>
       <c r="D9" s="5">
-        <v>0.011010000000000002</v>
+        <v>1.1010000000000002E-2</v>
       </c>
       <c r="E9" s="5">
-        <v>0.011466666666666667</v>
+        <v>1.1466666666666667E-2</v>
       </c>
       <c r="F9" s="5">
-        <v>76844.26229508201</v>
+        <v>76844.262295082008</v>
       </c>
       <c r="G9" s="5">
-        <v>0.0020827332469084405</v>
+        <v>2.0827332469084405E-3</v>
       </c>
       <c r="H9" s="5">
-        <v>0.9162641333333333</v>
+        <v>0.91626413333333334</v>
       </c>
       <c r="I9" s="5">
         <v>13692.252986413725</v>
       </c>
       <c r="J9" s="5">
-        <v>0.004934031470759392</v>
+        <v>4.9340314707593917E-3</v>
       </c>
       <c r="K9" s="5">
-        <v>6.476666666666667</v>
+        <v>6.4766666666666666</v>
       </c>
       <c r="L9" s="5">
         <v>7499.9999999996535</v>
       </c>
       <c r="M9" s="5">
-        <v>0.006666666666666821</v>
+        <v>6.6666666666668206E-3</v>
       </c>
       <c r="N9" s="5">
-        <f>10^-K9</f>
-      </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>3.3368242522829366E-7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>31</v>
       </c>
       <c r="B10" s="5">
-        <v>0.7085549999999999</v>
+        <v>0.70855499999999993</v>
       </c>
       <c r="C10" s="5">
         <v>2749.8189931647557</v>
       </c>
       <c r="D10" s="5">
-        <v>0.011010000000000039</v>
+        <v>1.1010000000000039E-2</v>
       </c>
       <c r="E10" s="5">
-        <v>0.011466666666666667</v>
+        <v>1.1466666666666667E-2</v>
       </c>
       <c r="F10" s="5">
         <v>19196.31430765292</v>
       </c>
       <c r="G10" s="5">
-        <v>0.004167066647468512</v>
+        <v>4.1670666474685116E-3</v>
       </c>
       <c r="H10" s="5">
         <v>0.9376987</v>
@@ -3077,64 +2998,65 @@
         <v>1179.3838578266912</v>
       </c>
       <c r="J10" s="5">
-        <v>0.016811705862384486</v>
+        <v>1.6811705862384486E-2</v>
       </c>
       <c r="K10" s="5">
         <v>6.496666666666667</v>
       </c>
       <c r="L10" s="5">
-        <v>30000.00000000128</v>
+        <v>30000.000000001281</v>
       </c>
       <c r="M10" s="5">
-        <v>0.0033333333333332624</v>
+        <v>3.3333333333332624E-3</v>
       </c>
       <c r="N10" s="5">
-        <f>10^-K10</f>
-      </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>3.1866424217867213E-7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>40</v>
       </c>
       <c r="B11" s="5">
-        <v>0.73608</v>
+        <v>0.73607999999999996</v>
       </c>
       <c r="C11" s="5">
         <v>282.03271724766904</v>
       </c>
       <c r="D11" s="5">
-        <v>0.034378713981183195</v>
+        <v>3.4378713981183195E-2</v>
       </c>
       <c r="E11" s="5">
-        <v>0.002533333333333333</v>
+        <v>2.5333333333333332E-3</v>
       </c>
       <c r="F11" s="5">
         <v>453857.79122541606</v>
       </c>
       <c r="G11" s="5">
-        <v>0.0008569973421454961</v>
+        <v>8.5699734214549615E-4</v>
       </c>
       <c r="H11" s="5">
-        <v>0.9753085333333334</v>
+        <v>0.97530853333333345</v>
       </c>
       <c r="I11" s="5">
-        <v>3820.796019851003</v>
+        <v>3820.7960198510032</v>
       </c>
       <c r="J11" s="5">
-        <v>0.009340334857904047</v>
+        <v>9.3403348579040469E-3</v>
       </c>
       <c r="K11" s="5">
-        <v>6.483333333333334</v>
+        <v>6.4833333333333343</v>
       </c>
       <c r="L11" s="5">
-        <v>30000.00000000128</v>
+        <v>30000.000000001281</v>
       </c>
       <c r="M11" s="5">
-        <v>0.0033333333333332624</v>
+        <v>3.3333333333332624E-3</v>
       </c>
       <c r="N11" s="5">
-        <f>10^-K11</f>
+        <f t="shared" si="0"/>
+        <v>3.28599324760064E-7</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>16</v>
@@ -3146,32 +3068,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="14.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="14" width="14.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -3217,7 +3127,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>0</v>
       </c>
@@ -3225,13 +3135,13 @@
         <v>0.22191300000000003</v>
       </c>
       <c r="C2" s="5">
-        <v>274981.8993164774</v>
+        <v>274981.89931647741</v>
       </c>
       <c r="D2" s="5">
-        <v>0.0011010000000000002</v>
+        <v>1.1010000000000002E-3</v>
       </c>
       <c r="E2" s="5">
-        <v>5.619666666666667</v>
+        <v>5.6196666666666673</v>
       </c>
       <c r="F2" s="5">
         <v>1.7101459785738076</v>
@@ -3246,23 +3156,23 @@
         <v>4024.5856032312045</v>
       </c>
       <c r="J2" s="5">
-        <v>0.009100783604784368</v>
+        <v>9.1007836047843679E-3</v>
       </c>
       <c r="K2" s="5">
-        <v>4.433333333333334</v>
+        <v>4.4333333333333336</v>
       </c>
       <c r="L2" s="5">
         <v>29999.999999995947</v>
       </c>
       <c r="M2" s="5">
-        <v>0.0033333333333335586</v>
+        <v>3.3333333333335586E-3</v>
       </c>
       <c r="N2" s="5">
-        <f>10^-K2</f>
-      </c>
-      <c r="O2" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+        <f t="shared" ref="N2:N11" si="0">10^-K2</f>
+        <v>3.6869450645195723E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>3.5</v>
       </c>
@@ -3270,10 +3180,10 @@
         <v>0.23072100000000004</v>
       </c>
       <c r="C3" s="5">
-        <v>91660.63310549247</v>
+        <v>91660.633105492467</v>
       </c>
       <c r="D3" s="5">
-        <v>0.0019069879391333342</v>
+        <v>1.9069879391333342E-3</v>
       </c>
       <c r="E3" s="5">
         <v>5.9868999999999994</v>
@@ -3285,74 +3195,74 @@
         <v>0.13943867230195997</v>
       </c>
       <c r="H3" s="5">
-        <v>0.9924900333333334</v>
+        <v>0.99249003333333341</v>
       </c>
       <c r="I3" s="5">
         <v>1031.3536899817057</v>
       </c>
       <c r="J3" s="5">
-        <v>0.017977759209120297</v>
+        <v>1.7977759209120297E-2</v>
       </c>
       <c r="K3" s="5">
-        <v>4.406666666666667</v>
+        <v>4.4066666666666672</v>
       </c>
       <c r="L3" s="5">
-        <v>4285.714285714196</v>
+        <v>4285.7142857141962</v>
       </c>
       <c r="M3" s="5">
-        <v>0.00881917103688206</v>
+        <v>8.8191710368820606E-3</v>
       </c>
       <c r="N3" s="5">
-        <f>10^-K3</f>
-      </c>
-      <c r="O3" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>3.9204266552701453E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>7</v>
       </c>
       <c r="B4" s="5">
-        <v>0.232923</v>
+        <v>0.23292299999999999</v>
       </c>
       <c r="C4" s="5">
-        <v>68745.47482911935</v>
+        <v>68745.474829119354</v>
       </c>
       <c r="D4" s="5">
-        <v>0.0022020000000000004</v>
+        <v>2.2020000000000004E-3</v>
       </c>
       <c r="E4" s="5">
-        <v>5.116133333333334</v>
+        <v>5.1161333333333339</v>
       </c>
       <c r="F4" s="5">
         <v>69.60800714827856</v>
       </c>
       <c r="G4" s="5">
-        <v>0.06920058606045973</v>
+        <v>6.9200586060459729E-2</v>
       </c>
       <c r="H4" s="5">
-        <v>0.9890856666666666</v>
+        <v>0.98908566666666664</v>
       </c>
       <c r="I4" s="5">
-        <v>10050.12244064676</v>
+        <v>10050.122440646761</v>
       </c>
       <c r="J4" s="5">
-        <v>0.005759087755404003</v>
+        <v>5.7590877554040028E-3</v>
       </c>
       <c r="K4" s="5">
-        <v>4.406666666666667</v>
+        <v>4.4066666666666672</v>
       </c>
       <c r="L4" s="5">
-        <v>4285.714285714196</v>
+        <v>4285.7142857141962</v>
       </c>
       <c r="M4" s="5">
-        <v>0.00881917103688206</v>
+        <v>8.8191710368820606E-3</v>
       </c>
       <c r="N4" s="5">
-        <f>10^-K4</f>
-      </c>
-      <c r="O4" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>3.9204266552701453E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>16</v>
       </c>
@@ -3360,55 +3270,55 @@
         <v>0.241731</v>
       </c>
       <c r="C5" s="5">
-        <v>274981.8993164774</v>
+        <v>274981.89931647741</v>
       </c>
       <c r="D5" s="5">
-        <v>0.0011010000000000002</v>
+        <v>1.1010000000000002E-3</v>
       </c>
       <c r="E5" s="5">
-        <v>6.061066666666666</v>
+        <v>6.0610666666666662</v>
       </c>
       <c r="F5" s="5">
         <v>1.0624985293249567</v>
       </c>
       <c r="G5" s="5">
-        <v>0.5601124212552719</v>
+        <v>0.56011242125527194</v>
       </c>
       <c r="H5" s="5">
-        <v>0.9606208666666666</v>
+        <v>0.96062086666666657</v>
       </c>
       <c r="I5" s="5">
-        <v>4639.514131168303</v>
+        <v>4639.5141311683028</v>
       </c>
       <c r="J5" s="5">
-        <v>0.008476237593479248</v>
+        <v>8.4762375934792477E-3</v>
       </c>
       <c r="K5" s="5">
-        <v>4.409999999999999</v>
+        <v>4.4099999999999993</v>
       </c>
       <c r="L5" s="5">
         <v>3333.333333333278</v>
       </c>
       <c r="M5" s="5">
-        <v>0.010000000000000083</v>
+        <v>1.0000000000000083E-2</v>
       </c>
       <c r="N5" s="5">
-        <f>10^-K5</f>
-      </c>
-      <c r="O5" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>3.8904514499428107E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>19.5</v>
       </c>
       <c r="B6" s="5">
-        <v>0.247236</v>
+        <v>0.24723600000000001</v>
       </c>
       <c r="C6" s="5">
-        <v>91660.63310549247</v>
+        <v>91660.633105492467</v>
       </c>
       <c r="D6" s="5">
-        <v>0.0019069879391333342</v>
+        <v>1.9069879391333342E-3</v>
       </c>
       <c r="E6" s="5">
         <v>5.822966666666666</v>
@@ -3417,7 +3327,7 @@
         <v>174.32829853837376</v>
       </c>
       <c r="G6" s="5">
-        <v>0.04372757838151008</v>
+        <v>4.3727578381510077E-2</v>
       </c>
       <c r="H6" s="5">
         <v>1.0164133333333334</v>
@@ -3426,7 +3336,7 @@
         <v>413.35788960235146</v>
       </c>
       <c r="J6" s="5">
-        <v>0.028397248179963527</v>
+        <v>2.8397248179963527E-2</v>
       </c>
       <c r="K6" s="5">
         <v>4.3999999999999995</v>
@@ -3435,14 +3345,14 @@
         <v>3333.333333333278</v>
       </c>
       <c r="M6" s="5">
-        <v>0.010000000000000083</v>
+        <v>1.0000000000000083E-2</v>
       </c>
       <c r="N6" s="5">
-        <f>10^-K6</f>
-      </c>
-      <c r="O6" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>3.9810717055349701E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>23</v>
       </c>
@@ -3450,28 +3360,28 @@
         <v>0.25274100000000005</v>
       </c>
       <c r="C7" s="5">
-        <v>68745.47482911935</v>
+        <v>68745.474829119354</v>
       </c>
       <c r="D7" s="5">
-        <v>0.0022020000000000004</v>
+        <v>2.2020000000000004E-3</v>
       </c>
       <c r="E7" s="5">
-        <v>5.352633333333333</v>
+        <v>5.3526333333333334</v>
       </c>
       <c r="F7" s="5">
-        <v>1.386770475003889</v>
+        <v>1.3867704750038889</v>
       </c>
       <c r="G7" s="5">
         <v>0.49027198687168505</v>
       </c>
       <c r="H7" s="5">
-        <v>0.9370814333333334</v>
+        <v>0.93708143333333338</v>
       </c>
       <c r="I7" s="5">
         <v>154.37222059413017</v>
       </c>
       <c r="J7" s="5">
-        <v>0.04646808733720141</v>
+        <v>4.6468087337201411E-2</v>
       </c>
       <c r="K7" s="5">
         <v>4.3999999999999995</v>
@@ -3480,14 +3390,14 @@
         <v>3333.333333333278</v>
       </c>
       <c r="M7" s="5">
-        <v>0.010000000000000083</v>
+        <v>1.0000000000000083E-2</v>
       </c>
       <c r="N7" s="5">
-        <f>10^-K7</f>
-      </c>
-      <c r="O7" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>3.9810717055349701E-5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>24</v>
       </c>
@@ -3498,7 +3408,7 @@
         <v>39283.12847378249</v>
       </c>
       <c r="D8" s="5">
-        <v>0.0029129721934821147</v>
+        <v>2.9129721934821147E-3</v>
       </c>
       <c r="E8" s="5">
         <v>5.5540666666666665</v>
@@ -3510,58 +3420,58 @@
         <v>0.36661049872825213</v>
       </c>
       <c r="H8" s="5">
-        <v>0.9820656666666666</v>
+        <v>0.98206566666666661</v>
       </c>
       <c r="I8" s="5">
         <v>2684.4235001559855</v>
       </c>
       <c r="J8" s="5">
-        <v>0.01114330086828456</v>
+        <v>1.1143300868284561E-2</v>
       </c>
       <c r="K8" s="5">
-        <v>4.433333333333334</v>
+        <v>4.4333333333333336</v>
       </c>
       <c r="L8" s="5">
         <v>29999.999999995947</v>
       </c>
       <c r="M8" s="5">
-        <v>0.0033333333333335586</v>
+        <v>3.3333333333335586E-3</v>
       </c>
       <c r="N8" s="5">
-        <f>10^-K8</f>
-      </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>3.6869450645195723E-5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>27.5</v>
       </c>
       <c r="B9" s="5">
-        <v>0.254943</v>
+        <v>0.25494299999999998</v>
       </c>
       <c r="C9" s="5">
-        <v>68745.47482911935</v>
+        <v>68745.474829119354</v>
       </c>
       <c r="D9" s="5">
-        <v>0.0022020000000000004</v>
+        <v>2.2020000000000004E-3</v>
       </c>
       <c r="E9" s="5">
         <v>5.2942</v>
       </c>
       <c r="F9" s="5">
-        <v>3.618990245988923</v>
+        <v>3.6189902459889232</v>
       </c>
       <c r="G9" s="5">
-        <v>0.3034908949759996</v>
+        <v>0.30349089497599963</v>
       </c>
       <c r="H9" s="5">
-        <v>0.9822683666666666</v>
+        <v>0.98226836666666661</v>
       </c>
       <c r="I9" s="5">
         <v>8471.835726141444</v>
       </c>
       <c r="J9" s="5">
-        <v>0.006272643560024048</v>
+        <v>6.2726435600240476E-3</v>
       </c>
       <c r="K9" s="5">
         <v>4.43</v>
@@ -3570,25 +3480,25 @@
         <v>9999.999999999538</v>
       </c>
       <c r="M9" s="5">
-        <v>0.0057735026918963915</v>
+        <v>5.7735026918963915E-3</v>
       </c>
       <c r="N9" s="5">
-        <f>10^-K9</f>
-      </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>3.7153522909717237E-5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>31</v>
       </c>
       <c r="B10" s="5">
-        <v>0.259347</v>
+        <v>0.25934699999999999</v>
       </c>
       <c r="C10" s="5">
-        <v>17186.36870727984</v>
+        <v>17186.368707279838</v>
       </c>
       <c r="D10" s="5">
-        <v>0.004404000000000001</v>
+        <v>4.4040000000000008E-3</v>
       </c>
       <c r="E10" s="5">
         <v>5.0118</v>
@@ -3597,16 +3507,16 @@
         <v>3.3516263984954406</v>
       </c>
       <c r="G10" s="5">
-        <v>0.3153636049599468</v>
+        <v>0.31536360495994681</v>
       </c>
       <c r="H10" s="5">
-        <v>0.9360120333333333</v>
+        <v>0.93601203333333327</v>
       </c>
       <c r="I10" s="5">
-        <v>740.169869090604</v>
+        <v>740.16986909060404</v>
       </c>
       <c r="J10" s="5">
-        <v>0.021221382424521203</v>
+        <v>2.1221382424521203E-2</v>
       </c>
       <c r="K10" s="5">
         <v>4.43</v>
@@ -3615,28 +3525,28 @@
         <v>9999.999999999538</v>
       </c>
       <c r="M10" s="5">
-        <v>0.0057735026918963915</v>
+        <v>5.7735026918963915E-3</v>
       </c>
       <c r="N10" s="5">
-        <f>10^-K10</f>
-      </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>3.7153522909717237E-5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>40</v>
       </c>
       <c r="B11" s="5">
-        <v>0.263751</v>
+        <v>0.26375100000000001</v>
       </c>
       <c r="C11" s="5">
         <v>22915.158276373117</v>
       </c>
       <c r="D11" s="5">
-        <v>0.0038139758782666684</v>
+        <v>3.8139758782666684E-3</v>
       </c>
       <c r="E11" s="5">
-        <v>4.809033333333333</v>
+        <v>4.8090333333333328</v>
       </c>
       <c r="F11" s="5">
         <v>10.482899665092319</v>
@@ -3651,7 +3561,7 @@
         <v>1227.8930672395968</v>
       </c>
       <c r="J11" s="5">
-        <v>0.0164762775407891</v>
+        <v>1.6476277540789099E-2</v>
       </c>
       <c r="K11" s="5">
         <v>4.41</v>
@@ -3660,10 +3570,11 @@
         <v>2499.9999999999955</v>
       </c>
       <c r="M11" s="5">
-        <v>0.011547005383792526</v>
+        <v>1.1547005383792526E-2</v>
       </c>
       <c r="N11" s="5">
-        <f>10^-K11</f>
+        <f t="shared" si="0"/>
+        <v>3.8904514499428046E-5</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>15</v>
@@ -3675,28 +3586,22 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="5" width="14.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="14.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3712,7 +3617,7 @@
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -3724,51 +3629,50 @@
       <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row r="2" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>0</v>
       </c>
       <c r="B2" s="5">
-        <v>0.223014</v>
+        <v>0.22301399999999999</v>
       </c>
       <c r="C2" s="5">
-        <v>0.0011010000000000002</v>
+        <v>1.1010000000000002E-3</v>
       </c>
       <c r="D2" s="5">
-        <v>5.922366666666666</v>
+        <v>5.9223666666666661</v>
       </c>
       <c r="E2" s="5">
-        <v>0.067418131422077</v>
-      </c>
-      <c r="F2" s="13">
+        <v>6.7418131422077004E-2</v>
+      </c>
+      <c r="F2" s="12">
         <v>1.0266189000000001</v>
       </c>
       <c r="G2" s="5">
-        <v>0.02152490883983794</v>
+        <v>2.1524908839837941E-2</v>
       </c>
       <c r="H2" s="5">
-        <v>7.183333333333334</v>
+        <v>7.1833333333333336</v>
       </c>
       <c r="I2" s="5">
-        <v>0.006666666666666821</v>
-      </c>
-      <c r="J2" s="14">
-        <f>10^-H2</f>
-      </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="13">
+        <v>6.6666666666668206E-3</v>
+      </c>
+      <c r="J2" s="13">
+        <f t="shared" ref="J2:J11" si="0">10^-H2</f>
+        <v>6.5564184941797799E-8</v>
+      </c>
+      <c r="L2" s="12">
         <v>1.0266189000000001</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row r="3" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>7</v>
       </c>
@@ -3776,35 +3680,35 @@
         <v>0.25384200000000007</v>
       </c>
       <c r="C3" s="5">
-        <v>0.003303000000000001</v>
+        <v>3.3030000000000008E-3</v>
       </c>
       <c r="D3" s="5">
-        <v>5.939766666666666</v>
+        <v>5.9397666666666664</v>
       </c>
       <c r="E3" s="5">
-        <v>0.044008572397255016</v>
-      </c>
-      <c r="F3" s="13">
-        <v>0.9814482666666665</v>
+        <v>4.4008572397255016E-2</v>
+      </c>
+      <c r="F3" s="12">
+        <v>0.98144826666666651</v>
       </c>
       <c r="G3" s="5">
-        <v>0.012645879700167591</v>
+        <v>1.2645879700167591E-2</v>
       </c>
       <c r="H3" s="5">
-        <v>7.113333333333333</v>
+        <v>7.1133333333333333</v>
       </c>
       <c r="I3" s="5">
-        <v>0.0033333333333332624</v>
-      </c>
-      <c r="J3" s="14">
-        <f>10^-H3</f>
-      </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="13">
-        <v>0.9814482666666665</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+        <v>3.3333333333332624E-3</v>
+      </c>
+      <c r="J3" s="13">
+        <f t="shared" si="0"/>
+        <v>7.7031200579721308E-8</v>
+      </c>
+      <c r="L3" s="12">
+        <v>0.98144826666666651</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>16</v>
       </c>
@@ -3812,35 +3716,35 @@
         <v>0.48835500000000004</v>
       </c>
       <c r="C4" s="5">
-        <v>0.009534939695666655</v>
+        <v>9.5349396956666554E-3</v>
       </c>
       <c r="D4" s="5">
-        <v>5.317733333333334</v>
+        <v>5.3177333333333339</v>
       </c>
       <c r="E4" s="5">
-        <v>0.030120996737233625</v>
-      </c>
-      <c r="F4" s="13">
-        <v>0.9563208</v>
+        <v>3.0120996737233625E-2</v>
+      </c>
+      <c r="F4" s="12">
+        <v>0.95632079999999997</v>
       </c>
       <c r="G4" s="5">
-        <v>0.013212656266751709</v>
+        <v>1.3212656266751709E-2</v>
       </c>
       <c r="H4" s="5">
         <v>6.830000000000001</v>
       </c>
       <c r="I4" s="5">
-        <v>6.2803698347351e-16</v>
-      </c>
-      <c r="J4" s="14">
-        <f>10^-H4</f>
-      </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="13">
-        <v>0.9563208</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+        <v>6.2803698347350997E-16</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" si="0"/>
+        <v>1.4791083881682016E-7</v>
+      </c>
+      <c r="L4" s="12">
+        <v>0.95632079999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>27.5</v>
       </c>
@@ -3848,71 +3752,71 @@
         <v>1.0278450000000001</v>
       </c>
       <c r="C5" s="5">
-        <v>0.042995424465866156</v>
+        <v>4.2995424465866156E-2</v>
       </c>
       <c r="D5" s="5">
         <v>4.2885</v>
       </c>
       <c r="E5" s="5">
-        <v>0.02594635491419437</v>
-      </c>
-      <c r="F5" s="13">
-        <v>0.9399317666666667</v>
+        <v>2.5946354914194371E-2</v>
+      </c>
+      <c r="F5" s="12">
+        <v>0.93993176666666667</v>
       </c>
       <c r="G5" s="5">
-        <v>0.03278037849661158</v>
+        <v>3.2780378496611577E-2</v>
       </c>
       <c r="H5" s="5">
-        <v>6.510000000000001</v>
+        <v>6.5100000000000007</v>
       </c>
       <c r="I5" s="5">
-        <v>6.2803698347351e-16</v>
-      </c>
-      <c r="J5" s="14">
-        <f>10^-H5</f>
-      </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="13">
-        <v>0.9399317666666667</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+        <v>6.2803698347350997E-16</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="0"/>
+        <v>3.0902954325135797E-7</v>
+      </c>
+      <c r="L5" s="12">
+        <v>0.93993176666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>40</v>
       </c>
       <c r="B6" s="5">
-        <v>0.91224</v>
+        <v>0.91224000000000005</v>
       </c>
       <c r="C6" s="5">
-        <v>0.014564860967410588</v>
+        <v>1.4564860967410588E-2</v>
       </c>
       <c r="D6" s="5">
         <v>4.3985666666666665</v>
       </c>
       <c r="E6" s="5">
-        <v>0.0675168456345856</v>
-      </c>
-      <c r="F6" s="15">
-        <v>0.9689079666666668</v>
+        <v>6.7516845634585598E-2</v>
+      </c>
+      <c r="F6" s="14">
+        <v>0.96890796666666679</v>
       </c>
       <c r="G6" s="5">
-        <v>0.012248600656038687</v>
+        <v>1.2248600656038687E-2</v>
       </c>
       <c r="H6" s="5">
-        <v>6.516666666666666</v>
+        <v>6.5166666666666657</v>
       </c>
       <c r="I6" s="5">
-        <v>0.006666666666666821</v>
-      </c>
-      <c r="J6" s="14">
-        <f>10^-H6</f>
-      </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="15">
-        <v>0.9689079666666668</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+        <v>6.6666666666668206E-3</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="0"/>
+        <v>3.0432198871077237E-7</v>
+      </c>
+      <c r="L6" s="14">
+        <v>0.96890796666666679</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>51.5</v>
       </c>
@@ -3920,16 +3824,17 @@
         <v>1.005825</v>
       </c>
       <c r="C7" s="5">
-        <v>0.029129721934821176</v>
+        <v>2.9129721934821176E-2</v>
       </c>
       <c r="D7" s="5">
         <v>3.9207666666666667</v>
       </c>
       <c r="E7" s="5">
-        <v>0.09620250054500204</v>
-      </c>
-      <c r="F7" s="15">
+        <v>9.620250054500204E-2</v>
+      </c>
+      <c r="F7" s="14">
         <f>AVERAGE(F6,F8)</f>
+        <v>0.93433823333333343</v>
       </c>
       <c r="G7" s="5">
         <v>0.14177843598383005</v>
@@ -3938,17 +3843,17 @@
         <v>6.496666666666667</v>
       </c>
       <c r="I7" s="5">
-        <v>0.0033333333333332624</v>
-      </c>
-      <c r="J7" s="14">
-        <f>10^-H7</f>
-      </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="15">
+        <v>3.3333333333332624E-3</v>
+      </c>
+      <c r="J7" s="13">
+        <f t="shared" si="0"/>
+        <v>3.1866424217867213E-7</v>
+      </c>
+      <c r="L7" s="14">
         <v>1.0654959333333334</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+    <row r="8" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>64</v>
       </c>
@@ -3956,71 +3861,71 @@
         <v>1.1049149999999999</v>
       </c>
       <c r="C8" s="5">
-        <v>0.04703474061797295</v>
+        <v>4.7034740617972949E-2</v>
       </c>
       <c r="D8" s="5">
-        <v>4.176433333333333</v>
+        <v>4.1764333333333328</v>
       </c>
       <c r="E8" s="5">
-        <v>0.03272289378673253</v>
-      </c>
-      <c r="F8" s="13">
-        <v>0.8997685</v>
+        <v>3.2722893786732529E-2</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0.89976849999999997</v>
       </c>
       <c r="G8" s="5">
-        <v>0.00821035720721089</v>
+        <v>8.2103572072108905E-3</v>
       </c>
       <c r="H8" s="5">
-        <v>6.510000000000001</v>
+        <v>6.5100000000000007</v>
       </c>
       <c r="I8" s="5">
-        <v>6.2803698347351e-16</v>
-      </c>
-      <c r="J8" s="14">
-        <f>10^-H8</f>
-      </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="13">
-        <v>0.8997685</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+        <v>6.2803698347350997E-16</v>
+      </c>
+      <c r="J8" s="13">
+        <f t="shared" si="0"/>
+        <v>3.0902954325135797E-7</v>
+      </c>
+      <c r="L8" s="12">
+        <v>0.89976849999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>75.5</v>
       </c>
       <c r="B9" s="5">
-        <v>1.14345</v>
+        <v>1.1434500000000001</v>
       </c>
       <c r="C9" s="5">
-        <v>0.038534999999999986</v>
+        <v>3.8534999999999986E-2</v>
       </c>
       <c r="D9" s="5">
-        <v>3.6613</v>
+        <v>3.6613000000000002</v>
       </c>
       <c r="E9" s="5">
-        <v>0.04058883261850885</v>
-      </c>
-      <c r="F9" s="15">
-        <v>0.9534774666666667</v>
+        <v>4.0588832618508847E-2</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0.95347746666666666</v>
       </c>
       <c r="G9" s="5">
-        <v>0.0007209760891396707</v>
+        <v>7.2097608913967071E-4</v>
       </c>
       <c r="H9" s="5">
         <v>6.3933333333333335</v>
       </c>
       <c r="I9" s="5">
-        <v>0.006666666666666821</v>
-      </c>
-      <c r="J9" s="14">
-        <f>10^-H9</f>
-      </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="15">
-        <v>0.9534774666666667</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+        <v>6.6666666666668206E-3</v>
+      </c>
+      <c r="J9" s="13">
+        <f t="shared" si="0"/>
+        <v>4.0426548736234359E-7</v>
+      </c>
+      <c r="L9" s="14">
+        <v>0.95347746666666666</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>88</v>
       </c>
@@ -4028,35 +3933,35 @@
         <v>1.2040050000000002</v>
       </c>
       <c r="C10" s="5">
-        <v>0.02752500000000002</v>
+        <v>2.7525000000000022E-2</v>
       </c>
       <c r="D10" s="5">
-        <v>3.8012</v>
+        <v>3.8012000000000001</v>
       </c>
       <c r="E10" s="5">
-        <v>0.026439427628701346</v>
-      </c>
-      <c r="F10" s="15">
-        <v>0.9278216666666665</v>
+        <v>2.6439427628701346E-2</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0.92782166666666654</v>
       </c>
       <c r="G10" s="5">
-        <v>0.0035484659602582165</v>
+        <v>3.5484659602582165E-3</v>
       </c>
       <c r="H10" s="5">
-        <v>6.463333333333334</v>
+        <v>6.4633333333333338</v>
       </c>
       <c r="I10" s="5">
-        <v>0.00881917103688206</v>
-      </c>
-      <c r="J10" s="14">
-        <f>10^-H10</f>
-      </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="15">
-        <v>0.9278216666666665</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+        <v>8.8191710368820606E-3</v>
+      </c>
+      <c r="J10" s="13">
+        <f t="shared" si="0"/>
+        <v>3.440857338265124E-7</v>
+      </c>
+      <c r="L10" s="14">
+        <v>0.92782166666666654</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>99.5</v>
       </c>
@@ -4064,7 +3969,7 @@
         <v>1.192995</v>
       </c>
       <c r="C11" s="5">
-        <v>0.030650542817379306</v>
+        <v>3.0650542817379306E-2</v>
       </c>
       <c r="D11" s="5">
         <v>3.2709333333333332</v>
@@ -4072,24 +3977,25 @@
       <c r="E11" s="5">
         <v>0.16515569758396006</v>
       </c>
-      <c r="F11" s="13">
-        <v>0.9482218666666666</v>
+      <c r="F11" s="12">
+        <v>0.94822186666666664</v>
       </c>
       <c r="G11" s="5">
-        <v>0.017242691340713382</v>
+        <v>1.7242691340713382E-2</v>
       </c>
       <c r="H11" s="5">
-        <v>6.383333333333333</v>
+        <v>6.3833333333333329</v>
       </c>
       <c r="I11" s="5">
-        <v>0.0033333333333332624</v>
-      </c>
-      <c r="J11" s="14">
-        <f>10^-H11</f>
+        <v>3.3333333333332624E-3</v>
+      </c>
+      <c r="J11" s="13">
+        <f t="shared" si="0"/>
+        <v>4.1368204023885066E-7</v>
       </c>
       <c r="K11" s="6"/>
-      <c r="L11" s="13">
-        <v>0.9482218666666666</v>
+      <c r="L11" s="12">
+        <v>0.94822186666666664</v>
       </c>
     </row>
   </sheetData>
@@ -4098,27 +4004,18 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="10" width="14.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row r="1" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4149,9 +4046,8 @@
       <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    </row>
+    <row r="2" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>0</v>
       </c>
@@ -4159,32 +4055,32 @@
         <v>0.22191300000000003</v>
       </c>
       <c r="C2" s="5">
-        <v>0.0011010000000000002</v>
+        <v>1.1010000000000002E-3</v>
       </c>
       <c r="D2" s="5">
         <v>5.5113666666666665</v>
       </c>
       <c r="E2" s="5">
-        <v>0.044581062247451154</v>
+        <v>4.4581062247451154E-2</v>
       </c>
       <c r="F2" s="5">
-        <v>0.03169226666666666</v>
+        <v>3.1692266666666663E-2</v>
       </c>
       <c r="G2" s="5">
-        <v>0.0005875602389920916</v>
+        <v>5.8756023899209163E-4</v>
       </c>
       <c r="H2" s="5">
-        <v>7.096666666666667</v>
+        <v>7.0966666666666667</v>
       </c>
       <c r="I2" s="5">
-        <v>0.008819171036882005</v>
+        <v>8.819171036882005E-3</v>
       </c>
       <c r="J2" s="5">
-        <f>10^-G2</f>
-      </c>
-      <c r="K2" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+        <f t="shared" ref="J2:J11" si="0">10^-G2</f>
+        <v>0.99864800731916359</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>7</v>
       </c>
@@ -4192,145 +4088,145 @@
         <v>0.25274100000000005</v>
       </c>
       <c r="C3" s="5">
-        <v>0.0029129721934821147</v>
+        <v>2.9129721934821147E-3</v>
       </c>
       <c r="D3" s="5">
-        <v>5.520366666666667</v>
+        <v>5.5203666666666669</v>
       </c>
       <c r="E3" s="5">
-        <v>0.018004567321778134</v>
+        <v>1.8004567321778134E-2</v>
       </c>
       <c r="F3" s="5">
-        <v>0.028857133333333337</v>
+        <v>2.8857133333333337E-2</v>
       </c>
       <c r="G3" s="5">
-        <v>0.0006007187953702722</v>
+        <v>6.0071879537027223E-4</v>
       </c>
       <c r="H3" s="5">
         <v>7.0200000000000005</v>
       </c>
       <c r="I3" s="5">
-        <v>0.015275252316519432</v>
+        <v>1.5275252316519432E-2</v>
       </c>
       <c r="J3" s="5">
-        <f>10^-G3</f>
-      </c>
-      <c r="K3" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.99861775004539699</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>16</v>
       </c>
       <c r="B4" s="5">
-        <v>0.455325</v>
+        <v>0.45532499999999998</v>
       </c>
       <c r="C4" s="4">
         <v>0</v>
       </c>
       <c r="D4" s="5">
-        <v>5.143233333333333</v>
+        <v>5.1432333333333329</v>
       </c>
       <c r="E4" s="5">
-        <v>0.06928523973000644</v>
+        <v>6.9285239730006443E-2</v>
       </c>
       <c r="F4" s="5">
-        <v>0.005019866666666667</v>
+        <v>5.0198666666666667E-3</v>
       </c>
       <c r="G4" s="5">
-        <v>0.0008145732734246674</v>
+        <v>8.1457327342466742E-4</v>
       </c>
       <c r="H4" s="5">
         <v>6.8133333333333335</v>
       </c>
       <c r="I4" s="5">
-        <v>0.006666666666666821</v>
+        <v>6.6666666666668206E-3</v>
       </c>
       <c r="J4" s="5">
-        <f>10^-G4</f>
-      </c>
-      <c r="K4" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.99812613360745928</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>27.5</v>
       </c>
       <c r="B5" s="5">
-        <v>0.763605</v>
+        <v>0.76360499999999998</v>
       </c>
       <c r="C5" s="5">
-        <v>0.042995424465866156</v>
+        <v>4.2995424465866156E-2</v>
       </c>
       <c r="D5" s="5">
-        <v>4.328133333333334</v>
+        <v>4.3281333333333336</v>
       </c>
       <c r="E5" s="5">
-        <v>0.014462864323654855</v>
+        <v>1.4462864323654855E-2</v>
       </c>
       <c r="F5" s="5">
-        <v>0.000026466666666666665</v>
+        <v>2.6466666666666665E-5</v>
       </c>
       <c r="G5" s="5">
-        <v>0.000026466666666666665</v>
+        <v>2.6466666666666665E-5</v>
       </c>
       <c r="H5" s="5">
         <v>6.6433333333333335</v>
       </c>
       <c r="I5" s="5">
-        <v>0.0033333333333335586</v>
+        <v>3.3333333333335586E-3</v>
       </c>
       <c r="J5" s="5">
-        <f>10^-G5</f>
-      </c>
-      <c r="K5" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.99993906010478306</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>40</v>
       </c>
       <c r="B6" s="5">
-        <v>0.7580999999999999</v>
+        <v>0.75809999999999989</v>
       </c>
       <c r="C6" s="5">
-        <v>0.02912972193482115</v>
+        <v>2.9129721934821148E-2</v>
       </c>
       <c r="D6" s="5">
-        <v>4.308766666666667</v>
+        <v>4.3087666666666671</v>
       </c>
       <c r="E6" s="5">
-        <v>0.0745082172947684</v>
+        <v>7.4508217294768406E-2</v>
       </c>
       <c r="F6" s="5">
-        <v>0.000183</v>
+        <v>1.83E-4</v>
       </c>
       <c r="G6" s="5">
-        <v>0.00018300000000000003</v>
+        <v>1.8300000000000003E-4</v>
       </c>
       <c r="H6" s="5">
         <v>6.63</v>
       </c>
       <c r="I6" s="5">
-        <v>0.015275252316519626</v>
+        <v>1.5275252316519626E-2</v>
       </c>
       <c r="J6" s="5">
-        <f>10^-G6</f>
-      </c>
-      <c r="K6" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.99957871569314682</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>51.5</v>
       </c>
       <c r="B7" s="5">
-        <v>0.9617849999999999</v>
+        <v>0.96178499999999989</v>
       </c>
       <c r="C7" s="5">
-        <v>0.005504999999999982</v>
+        <v>5.5049999999999821E-3</v>
       </c>
       <c r="D7" s="5">
         <v>3.869733333333333</v>
       </c>
       <c r="E7" s="5">
-        <v>0.049679047673821086</v>
+        <v>4.9679047673821086E-2</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
@@ -4339,17 +4235,17 @@
         <v>0</v>
       </c>
       <c r="H7" s="5">
-        <v>6.633333333333333</v>
+        <v>6.6333333333333329</v>
       </c>
       <c r="I7" s="5">
-        <v>0.00881917103688206</v>
+        <v>8.8191710368820606E-3</v>
       </c>
       <c r="J7" s="4">
-        <f>10^-G7</f>
-      </c>
-      <c r="K7" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>64</v>
       </c>
@@ -4357,32 +4253,32 @@
         <v>1.049865</v>
       </c>
       <c r="C8" s="5">
-        <v>0.07627951756533372</v>
+        <v>7.6279517565333715E-2</v>
       </c>
       <c r="D8" s="5">
-        <v>3.989066666666666</v>
+        <v>3.9890666666666661</v>
       </c>
       <c r="E8" s="5">
         <v>0.25576058031769566</v>
       </c>
       <c r="F8" s="5">
-        <v>0.00007553333333333333</v>
+        <v>7.5533333333333331E-5</v>
       </c>
       <c r="G8" s="5">
-        <v>0.00007553333333333333</v>
+        <v>7.5533333333333331E-5</v>
       </c>
       <c r="H8" s="5">
         <v>6.63</v>
       </c>
       <c r="I8" s="5">
-        <v>0.005773502691896135</v>
+        <v>5.7735026918961348E-3</v>
       </c>
       <c r="J8" s="5">
-        <f>10^-G8</f>
-      </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.9998260931961841</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>75.5</v>
       </c>
@@ -4390,13 +4286,13 @@
         <v>1.005825</v>
       </c>
       <c r="C9" s="5">
-        <v>0.03065054281737933</v>
+        <v>3.065054281737933E-2</v>
       </c>
       <c r="D9" s="5">
-        <v>3.5893</v>
+        <v>3.5893000000000002</v>
       </c>
       <c r="E9" s="5">
-        <v>0.0711910340796742</v>
+        <v>7.1191034079674198E-2</v>
       </c>
       <c r="F9" s="4">
         <v>0</v>
@@ -4405,17 +4301,17 @@
         <v>0</v>
       </c>
       <c r="H9" s="5">
-        <v>6.546666666666667</v>
+        <v>6.5466666666666669</v>
       </c>
       <c r="I9" s="5">
-        <v>0.01452966314513578</v>
+        <v>1.452966314513578E-2</v>
       </c>
       <c r="J9" s="4">
-        <f>10^-G9</f>
-      </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>88</v>
       </c>
@@ -4423,13 +4319,13 @@
         <v>1.0278450000000001</v>
       </c>
       <c r="C10" s="5">
-        <v>0.061301085634758536</v>
+        <v>6.1301085634758536E-2</v>
       </c>
       <c r="D10" s="5">
         <v>3.5689666666666664</v>
       </c>
       <c r="E10" s="5">
-        <v>0.168777489941968</v>
+        <v>0.16877748994196801</v>
       </c>
       <c r="F10" s="4">
         <v>0</v>
@@ -4438,46 +4334,47 @@
         <v>0</v>
       </c>
       <c r="H10" s="5">
-        <v>6.596666666666667</v>
+        <v>6.5966666666666667</v>
       </c>
       <c r="I10" s="5">
-        <v>0.0033333333333332624</v>
+        <v>3.3333333333332624E-3</v>
       </c>
       <c r="J10" s="4">
-        <f>10^-G10</f>
-      </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>99.5</v>
       </c>
       <c r="B11" s="5">
-        <v>1.115925</v>
+        <v>1.1159250000000001</v>
       </c>
       <c r="C11" s="5">
-        <v>0.04156183856616547</v>
+        <v>4.1561838566165472E-2</v>
       </c>
       <c r="D11" s="5">
         <v>3.1640333333333337</v>
       </c>
       <c r="E11" s="5">
-        <v>0.09384104172008695</v>
+        <v>9.3841041720086948E-2</v>
       </c>
       <c r="F11" s="5">
-        <v>0.00007033333333333334</v>
+        <v>7.033333333333334E-5</v>
       </c>
       <c r="G11" s="5">
-        <v>0.00007033333333333334</v>
+        <v>7.033333333333334E-5</v>
       </c>
       <c r="H11" s="5">
         <v>6.54</v>
       </c>
       <c r="I11" s="5">
-        <v>0.005773502691896135</v>
+        <v>5.7735026918961348E-3</v>
       </c>
       <c r="J11" s="5">
-        <f>10^-G11</f>
+        <f t="shared" si="0"/>
+        <v>0.99983806462807412</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>10</v>
@@ -4489,27 +4386,20 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="10" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="8" width="14.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row r="1" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4534,15 +4424,14 @@
       <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    </row>
+    <row r="2" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>0</v>
       </c>
@@ -4550,145 +4439,145 @@
         <v>0.228519</v>
       </c>
       <c r="C2" s="5">
-        <v>0.0011010000000000002</v>
+        <v>1.1010000000000002E-3</v>
       </c>
       <c r="D2" s="5">
         <v>1.1317000000000002</v>
       </c>
       <c r="E2" s="5">
-        <v>0.022627490654806008</v>
+        <v>2.2627490654806008E-2</v>
       </c>
       <c r="F2" s="5">
-        <v>0.03661003333333333</v>
+        <v>3.6610033333333333E-2</v>
       </c>
       <c r="G2" s="5">
-        <v>0.0004375361407294753</v>
+        <v>4.3753614072947531E-4</v>
       </c>
       <c r="H2" s="5">
         <v>7.11</v>
       </c>
       <c r="I2" s="5">
-        <v>0.010000000000000083</v>
+        <v>1.0000000000000083E-2</v>
       </c>
       <c r="J2" s="5">
-        <f>10^-G2</f>
-      </c>
-      <c r="K2" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+        <f t="shared" ref="J2:J11" si="0">10^-G2</f>
+        <v>0.99899304312637893</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>7</v>
       </c>
       <c r="B3" s="5">
-        <v>0.256044</v>
+        <v>0.25604399999999999</v>
       </c>
       <c r="C3" s="5">
-        <v>0.0011010000000000002</v>
+        <v>1.1010000000000002E-3</v>
       </c>
       <c r="D3" s="5">
-        <v>1.0841</v>
+        <v>1.0841000000000001</v>
       </c>
       <c r="E3" s="5">
-        <v>0.018778800103662997</v>
+        <v>1.8778800103662997E-2</v>
       </c>
       <c r="F3" s="5">
-        <v>0.033173833333333326</v>
+        <v>3.3173833333333326E-2</v>
       </c>
       <c r="G3" s="5">
-        <v>0.0006307304266571505</v>
+        <v>6.307304266571505E-4</v>
       </c>
       <c r="H3" s="5">
-        <v>7.076666666666667</v>
+        <v>7.0766666666666671</v>
       </c>
       <c r="I3" s="5">
-        <v>0.0033333333333332624</v>
+        <v>3.3333333333332624E-3</v>
       </c>
       <c r="J3" s="5">
-        <f>10^-G3</f>
-      </c>
-      <c r="K3" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.99854874361439228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>17</v>
       </c>
       <c r="B4" s="5">
-        <v>0.59295</v>
+        <v>0.59294999999999998</v>
       </c>
       <c r="C4" s="5">
-        <v>0.005505000000000019</v>
+        <v>5.5050000000000194E-3</v>
       </c>
       <c r="D4" s="5">
         <v>0.5696</v>
       </c>
       <c r="E4" s="5">
-        <v>0.005708765190476856</v>
+        <v>5.7087651904768558E-3</v>
       </c>
       <c r="F4" s="5">
-        <v>0.0012198</v>
+        <v>1.2198000000000001E-3</v>
       </c>
       <c r="G4" s="5">
-        <v>0.00047800885277715665</v>
+        <v>4.7800885277715665E-4</v>
       </c>
       <c r="H4" s="5">
-        <v>6.773333333333333</v>
+        <v>6.7733333333333334</v>
       </c>
       <c r="I4" s="5">
-        <v>0.016666666666666607</v>
+        <v>1.6666666666666607E-2</v>
       </c>
       <c r="J4" s="5">
-        <f>10^-G4</f>
-      </c>
-      <c r="K4" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.99889994944098648</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>27.5</v>
       </c>
       <c r="B5" s="5">
-        <v>0.73608</v>
+        <v>0.73607999999999996</v>
       </c>
       <c r="C5" s="5">
-        <v>0.019069879391333342</v>
+        <v>1.9069879391333342E-2</v>
       </c>
       <c r="D5" s="5">
-        <v>0.07216666666666667</v>
+        <v>7.2166666666666671E-2</v>
       </c>
       <c r="E5" s="5">
-        <v>0.013915978026874174</v>
+        <v>1.3915978026874174E-2</v>
       </c>
       <c r="F5" s="5">
-        <v>0.0012325333333333334</v>
+        <v>1.2325333333333334E-3</v>
       </c>
       <c r="G5" s="5">
-        <v>0.0012002295646157772</v>
+        <v>1.2002295646157772E-3</v>
       </c>
       <c r="H5" s="5">
         <v>6.626666666666666</v>
       </c>
       <c r="I5" s="5">
-        <v>0.008819171036881781</v>
+        <v>8.8191710368817813E-3</v>
       </c>
       <c r="J5" s="5">
-        <f>10^-G5</f>
-      </c>
-      <c r="K5" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.99724018460816455</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>40</v>
       </c>
       <c r="B6" s="5">
-        <v>0.6700200000000001</v>
+        <v>0.67002000000000006</v>
       </c>
       <c r="C6" s="5">
-        <v>0.016514999999999985</v>
+        <v>1.6514999999999985E-2</v>
       </c>
       <c r="D6" s="5">
-        <v>0.06213333333333334</v>
+        <v>6.2133333333333339E-2</v>
       </c>
       <c r="E6" s="5">
-        <v>0.006933333333333304</v>
+        <v>6.9333333333333044E-3</v>
       </c>
       <c r="F6" s="4">
         <v>0</v>
@@ -4700,47 +4589,47 @@
         <v>6.7299999999999995</v>
       </c>
       <c r="I6" s="5">
-        <v>0.0057735026918963915</v>
+        <v>5.7735026918963915E-3</v>
       </c>
       <c r="J6" s="4">
-        <f>10^-G6</f>
-      </c>
-      <c r="K6" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>51.5</v>
       </c>
       <c r="B7" s="5">
-        <v>0.67002</v>
+        <v>0.67001999999999995</v>
       </c>
       <c r="C7" s="5">
-        <v>0.033030000000000004</v>
+        <v>3.3030000000000004E-2</v>
       </c>
       <c r="D7" s="5">
-        <v>0.0546</v>
+        <v>5.4600000000000003E-2</v>
       </c>
       <c r="E7" s="5">
-        <v>0.005671272637894704</v>
+        <v>5.6712726378947038E-3</v>
       </c>
       <c r="F7" s="5">
-        <v>0.00007273333333333333</v>
+        <v>7.273333333333333E-5</v>
       </c>
       <c r="G7" s="5">
-        <v>0.000039589617045101324</v>
+        <v>3.9589617045101324E-5</v>
       </c>
       <c r="H7" s="5">
-        <v>6.646666666666666</v>
+        <v>6.6466666666666656</v>
       </c>
       <c r="I7" s="5">
-        <v>0.0033333333333335586</v>
+        <v>3.3333333333335586E-3</v>
       </c>
       <c r="J7" s="5">
-        <f>10^-G7</f>
-      </c>
-      <c r="K7" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.99990884569276095</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>64</v>
       </c>
@@ -4748,98 +4637,98 @@
         <v>0.653505</v>
       </c>
       <c r="C8" s="5">
-        <v>0.02860481908699998</v>
+        <v>2.860481908699998E-2</v>
       </c>
       <c r="D8" s="5">
-        <v>0.05416666666666666</v>
+        <v>5.4166666666666662E-2</v>
       </c>
       <c r="E8" s="5">
-        <v>0.006833577231419741</v>
+        <v>6.8335772314197414E-3</v>
       </c>
       <c r="F8" s="5">
-        <v>0.0002572333333333333</v>
+        <v>2.5723333333333332E-4</v>
       </c>
       <c r="G8" s="5">
-        <v>0.000013443007269374084</v>
+        <v>1.3443007269374084E-5</v>
       </c>
       <c r="H8" s="5">
-        <v>6.756666666666667</v>
+        <v>6.7566666666666668</v>
       </c>
       <c r="I8" s="5">
-        <v>0.016666666666666607</v>
+        <v>1.6666666666666607E-2</v>
       </c>
       <c r="J8" s="5">
-        <f>10^-G8</f>
-      </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.99996904681091636</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>75.5</v>
       </c>
       <c r="B9" s="5">
-        <v>0.62598</v>
+        <v>0.62597999999999998</v>
       </c>
       <c r="C9" s="5">
-        <v>0.011009999999999964</v>
+        <v>1.1009999999999964E-2</v>
       </c>
       <c r="D9" s="5">
-        <v>0.04513333333333333</v>
+        <v>4.5133333333333331E-2</v>
       </c>
       <c r="E9" s="5">
-        <v>0.014723035616943197</v>
+        <v>1.4723035616943197E-2</v>
       </c>
       <c r="F9" s="5">
-        <v>0.00016063333333333333</v>
+        <v>1.6063333333333333E-4</v>
       </c>
       <c r="G9" s="5">
-        <v>0.00007309868519869409</v>
+        <v>7.3098685198694086E-5</v>
       </c>
       <c r="H9" s="5">
-        <v>6.713333333333334</v>
+        <v>6.7133333333333338</v>
       </c>
       <c r="I9" s="5">
-        <v>0.006666666666666525</v>
+        <v>6.6666666666665248E-3</v>
       </c>
       <c r="J9" s="5">
-        <f>10^-G9</f>
-      </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.99983169822147755</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>88</v>
       </c>
       <c r="B10" s="5">
-        <v>0.62598</v>
+        <v>0.62597999999999998</v>
       </c>
       <c r="C10" s="5">
-        <v>0.011009999999999964</v>
+        <v>1.1009999999999964E-2</v>
       </c>
       <c r="D10" s="5">
-        <v>0.03953333333333333</v>
+        <v>3.953333333333333E-2</v>
       </c>
       <c r="E10" s="5">
-        <v>0.01785733587197274</v>
+        <v>1.7857335871972739E-2</v>
       </c>
       <c r="F10" s="5">
-        <v>0.00028723333333333334</v>
+        <v>2.8723333333333334E-4</v>
       </c>
       <c r="G10" s="5">
-        <v>0.00008997555840955428</v>
+        <v>8.9975558409554279E-5</v>
       </c>
       <c r="H10" s="5">
         <v>6.72</v>
       </c>
       <c r="I10" s="5">
-        <v>0.0057735026918963915</v>
+        <v>5.7735026918963915E-3</v>
       </c>
       <c r="J10" s="5">
-        <f>10^-G10</f>
-      </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.99979284508001642</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>99.5</v>
       </c>
@@ -4847,19 +4736,19 @@
         <v>0.653505</v>
       </c>
       <c r="C11" s="5">
-        <v>0.009534939695666671</v>
+        <v>9.5349396956666711E-3</v>
       </c>
       <c r="D11" s="5">
-        <v>0.05940000000000001</v>
+        <v>5.9400000000000008E-2</v>
       </c>
       <c r="E11" s="5">
-        <v>0.0123289631897144</v>
+        <v>1.2328963189714401E-2</v>
       </c>
       <c r="F11" s="5">
-        <v>0.0003711</v>
+        <v>3.7110000000000002E-4</v>
       </c>
       <c r="G11" s="5">
-        <v>0.00004965913813186854</v>
+        <v>4.965913813186854E-5</v>
       </c>
       <c r="H11" s="5">
         <v>6.72</v>
@@ -4868,7 +4757,8 @@
         <v>0</v>
       </c>
       <c r="J11" s="5">
-        <f>10^-G11</f>
+        <f t="shared" si="0"/>
+        <v>0.99988566214587737</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>9</v>
@@ -4880,27 +4770,18 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="10" width="14.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row r="1" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4931,9 +4812,8 @@
       <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    </row>
+    <row r="2" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>0</v>
       </c>
@@ -4941,32 +4821,32 @@
         <v>0.22411499999999998</v>
       </c>
       <c r="C2" s="5">
-        <v>1.9626155733547187e-17</v>
+        <v>1.9626155733547187E-17</v>
       </c>
       <c r="D2" s="5">
         <v>1.0778666666666668</v>
       </c>
       <c r="E2" s="5">
-        <v>0.09684409005085287</v>
+        <v>9.6844090050852871E-2</v>
       </c>
       <c r="F2" s="5">
-        <v>0.9726913666666666</v>
+        <v>0.97269136666666656</v>
       </c>
       <c r="G2" s="5">
-        <v>0.057022565178542366</v>
+        <v>5.7022565178542366E-2</v>
       </c>
       <c r="H2" s="5">
-        <v>7.153333333333333</v>
+        <v>7.1533333333333333</v>
       </c>
       <c r="I2" s="5">
-        <v>0.0033333333333332624</v>
+        <v>3.3333333333332624E-3</v>
       </c>
       <c r="J2" s="5">
-        <f>10^-G2</f>
-      </c>
-      <c r="K2" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+        <f t="shared" ref="J2:J11" si="0">10^-G2</f>
+        <v>0.87695525490499737</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>7</v>
       </c>
@@ -4974,65 +4854,65 @@
         <v>0.26265000000000005</v>
       </c>
       <c r="C3" s="5">
-        <v>0.0011010000000000002</v>
+        <v>1.1010000000000002E-3</v>
       </c>
       <c r="D3" s="5">
-        <v>0.9814333333333334</v>
+        <v>0.98143333333333338</v>
       </c>
       <c r="E3" s="5">
-        <v>0.028883347759180826</v>
+        <v>2.8883347759180826E-2</v>
       </c>
       <c r="F3" s="5">
-        <v>0.9462143</v>
+        <v>0.94621429999999995</v>
       </c>
       <c r="G3" s="5">
-        <v>0.02644588383025483</v>
+        <v>2.644588383025483E-2</v>
       </c>
       <c r="H3" s="5">
-        <v>7.013333333333333</v>
+        <v>7.0133333333333328</v>
       </c>
       <c r="I3" s="5">
-        <v>0.012018504251546581</v>
+        <v>1.2018504251546581E-2</v>
       </c>
       <c r="J3" s="5">
-        <f>10^-G3</f>
-      </c>
-      <c r="K3" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.94092306841353668</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>24</v>
       </c>
       <c r="B4" s="5">
-        <v>0.818655</v>
+        <v>0.81865500000000002</v>
       </c>
       <c r="C4" s="5">
-        <v>0.01906987939133331</v>
+        <v>1.9069879391333311E-2</v>
       </c>
       <c r="D4" s="5">
-        <v>0.09436666666666667</v>
+        <v>9.4366666666666668E-2</v>
       </c>
       <c r="E4" s="5">
-        <v>0.016662266085713244</v>
+        <v>1.6662266085713244E-2</v>
       </c>
       <c r="F4" s="5">
-        <v>0.8522432666666667</v>
+        <v>0.85224326666666672</v>
       </c>
       <c r="G4" s="5">
-        <v>0.024703272343647976</v>
+        <v>2.4703272343647976E-2</v>
       </c>
       <c r="H4" s="5">
-        <v>6.636666666666667</v>
+        <v>6.6366666666666667</v>
       </c>
       <c r="I4" s="5">
-        <v>0.008819171036882005</v>
+        <v>8.819171036882005E-3</v>
       </c>
       <c r="J4" s="5">
-        <f>10^-G4</f>
-      </c>
-      <c r="K4" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.94470611748170974</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>31</v>
       </c>
@@ -5040,32 +4920,32 @@
         <v>1.1049149999999999</v>
       </c>
       <c r="C5" s="5">
-        <v>0.019848559771429186</v>
+        <v>1.9848559771429186E-2</v>
       </c>
       <c r="D5" s="5">
         <v>10.544666666666666</v>
       </c>
       <c r="E5" s="5">
-        <v>0.4614748253636862</v>
+        <v>0.46147482536368623</v>
       </c>
       <c r="F5" s="5">
-        <v>0.8767651333333334</v>
+        <v>0.87676513333333339</v>
       </c>
       <c r="G5" s="5">
-        <v>0.006453564251722533</v>
+        <v>6.4535642517225328E-3</v>
       </c>
       <c r="H5" s="5">
         <v>6.4433333333333325</v>
       </c>
       <c r="I5" s="5">
-        <v>0.04371625682868014</v>
+        <v>4.371625682868014E-2</v>
       </c>
       <c r="J5" s="5">
-        <f>10^-G5</f>
-      </c>
-      <c r="K5" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.98524998232887961</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>48</v>
       </c>
@@ -5073,7 +4953,7 @@
         <v>1.281075</v>
       </c>
       <c r="C6" s="5">
-        <v>0.02522707920073189</v>
+        <v>2.5227079200731889E-2</v>
       </c>
       <c r="D6" s="5">
         <v>10.098066666666666</v>
@@ -5085,119 +4965,119 @@
         <v>0.8275507666666666</v>
       </c>
       <c r="G6" s="5">
-        <v>0.024903518092987912</v>
+        <v>2.4903518092987912E-2</v>
       </c>
       <c r="H6" s="5">
         <v>6.419999999999999</v>
       </c>
       <c r="I6" s="5">
-        <v>0.009999999999999789</v>
+        <v>9.9999999999997886E-3</v>
       </c>
       <c r="J6" s="5">
-        <f>10^-G6</f>
-      </c>
-      <c r="K6" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.94427063007240564</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>55</v>
       </c>
       <c r="B7" s="5">
-        <v>1.31961</v>
+        <v>1.3196099999999999</v>
       </c>
       <c r="C7" s="5">
-        <v>0.029129721934821176</v>
+        <v>2.9129721934821176E-2</v>
       </c>
       <c r="D7" s="5">
         <v>10.912066666666666</v>
       </c>
       <c r="E7" s="5">
-        <v>0.2968621472071583</v>
+        <v>0.29686214720715831</v>
       </c>
       <c r="F7" s="5">
-        <v>0.8313750999999999</v>
+        <v>0.83137509999999992</v>
       </c>
       <c r="G7" s="5">
-        <v>0.009734851586096906</v>
+        <v>9.7348515860969063E-3</v>
       </c>
       <c r="H7" s="5">
         <v>6.32</v>
       </c>
       <c r="I7" s="5">
-        <v>0.0057735026918963915</v>
+        <v>5.7735026918963915E-3</v>
       </c>
       <c r="J7" s="5">
-        <f>10^-G7</f>
-      </c>
-      <c r="K7" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.97783403262099655</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>72</v>
       </c>
       <c r="B8" s="5">
-        <v>1.33062</v>
+        <v>1.3306199999999999</v>
       </c>
       <c r="C8" s="5">
-        <v>0.02522707920073189</v>
+        <v>2.5227079200731889E-2</v>
       </c>
       <c r="D8" s="5">
-        <v>9.4736</v>
+        <v>9.4735999999999994</v>
       </c>
       <c r="E8" s="5">
         <v>0.15701723896863468</v>
       </c>
       <c r="F8" s="5">
-        <v>0.8430381666666666</v>
+        <v>0.84303816666666664</v>
       </c>
       <c r="G8" s="5">
-        <v>0.021255799621541206</v>
+        <v>2.1255799621541206E-2</v>
       </c>
       <c r="H8" s="5">
-        <v>5.296666666666667</v>
+        <v>5.2966666666666669</v>
       </c>
       <c r="I8" s="5">
-        <v>0.05364492313143686</v>
+        <v>5.3644923131436859E-2</v>
       </c>
       <c r="J8" s="5">
-        <f>10^-G8</f>
-      </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.95223513194662701</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>79</v>
       </c>
       <c r="B9" s="5">
-        <v>1.35264</v>
+        <v>1.3526400000000001</v>
       </c>
       <c r="C9" s="5">
-        <v>0.01984855977142921</v>
+        <v>1.984855977142921E-2</v>
       </c>
       <c r="D9" s="5">
-        <v>9.539700000000002</v>
+        <v>9.5397000000000016</v>
       </c>
       <c r="E9" s="5">
-        <v>0.6284879951120788</v>
+        <v>0.62848799511207876</v>
       </c>
       <c r="F9" s="5">
-        <v>0.8676996333333333</v>
+        <v>0.86769963333333333</v>
       </c>
       <c r="G9" s="5">
-        <v>0.026098463036631953</v>
+        <v>2.6098463036631953E-2</v>
       </c>
       <c r="H9" s="5">
         <v>5.2</v>
       </c>
       <c r="I9" s="5">
-        <v>0.04509249752822887</v>
+        <v>4.5092497528228873E-2</v>
       </c>
       <c r="J9" s="5">
-        <f>10^-G9</f>
-      </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+        <f t="shared" si="0"/>
+        <v>0.94167607597083913</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>96</v>
       </c>
@@ -5205,61 +5085,62 @@
         <v>1.4352150000000001</v>
       </c>
       <c r="C10" s="5">
-        <v>0.02752500000000002</v>
+        <v>2.7525000000000022E-2</v>
       </c>
       <c r="D10" s="5">
         <v>9.541033333333333</v>
       </c>
       <c r="E10" s="5">
-        <v>0.8800704599317304</v>
+        <v>0.88007045993173039</v>
       </c>
       <c r="F10" s="5">
-        <v>0.8172242</v>
+        <v>0.81722419999999996</v>
       </c>
       <c r="G10" s="5">
-        <v>0.004579565729411476</v>
+        <v>4.5795657294114764E-3</v>
       </c>
       <c r="H10" s="5">
         <v>5.253333333333333</v>
       </c>
       <c r="I10" s="5">
-        <v>0.041766546953805564</v>
+        <v>4.1766546953805564E-2</v>
       </c>
       <c r="J10" s="5">
-        <f>10^-G10</f>
-      </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="20.25">
+        <f t="shared" si="0"/>
+        <v>0.98951056213629307</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>99.5</v>
       </c>
       <c r="B11" s="5">
-        <v>1.446225</v>
+        <v>1.4462250000000001</v>
       </c>
       <c r="C11" s="5">
-        <v>0.00953493969566664</v>
+        <v>9.5349396956666398E-3</v>
       </c>
       <c r="D11" s="5">
-        <v>8.523966666666666</v>
+        <v>8.5239666666666665</v>
       </c>
       <c r="E11" s="5">
         <v>0.21202690342920621</v>
       </c>
       <c r="F11" s="5">
-        <v>0.8863022333333334</v>
+        <v>0.88630223333333336</v>
       </c>
       <c r="G11" s="5">
-        <v>0.0012073440856322185</v>
+        <v>1.2073440856322185E-3</v>
       </c>
       <c r="H11" s="5">
-        <v>5.176666666666667</v>
+        <v>5.1766666666666667</v>
       </c>
       <c r="I11" s="5">
-        <v>0.04484541349024581</v>
+        <v>4.484541349024581E-2</v>
       </c>
       <c r="J11" s="5">
-        <f>10^-G11</f>
+        <f t="shared" si="0"/>
+        <v>0.99722384816265508</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>8</v>
